--- a/Noticias_Calcario_20260808.xlsx
+++ b/Noticias_Calcario_20260808.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D512"/>
+  <dimension ref="A1:D516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nitrogenados avançam e potássicos ficam estáveis - Agrolink</t>
+          <t>Nitrogenados avançam e potássicos ficam estáveis - agrolink.com.br</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Uberaba articula manifesto para defender empregos após hibernação da Mosaic - JM Online</t>
+          <t>Uberaba articula manifesto para defender empregos após hibernação da Mosaic - jmonline.com.br</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>05/08/2026 19:47</t>
+          <t>05/08/2026 20:12</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNa2xEVXdUTDV0aXY5bGlJTlNtSEdGODhlbHN5SE03Z2J4MEJyVTNCQ0RRZ0YtNmNnaDc0ZmwwYk4tV0xkRDlieFBDNEMyelp2Uk5xSFZDeDllOTlHeVUxa1BnTE5tT2ZmanVTcExpVGVJdlVTdEkwT1hVdlNSTjlHOG9MeDZMQWZJRXBoMjN6N0ROV2xTaEhvZjZfMzZaR1BfX0NPeGtTY3RUWTFoTkFGdU5iQWE4U0EzbVNUWU9n0gHGAUFVX3lxTFBfaFlpazg0ZWJoVjM4Z2NPd1daOWQwUWl0NW9QOURVNFNwcTVvMDNoZk9ncjJjUFhCeVQ5NldWblFlbW5ZbU9UWXBfWlBBZnNxWEo3bVp0bGtUVkc4T2hHWTh5dlRzeEprd29aYkE1ak1qUlV3N19Kd1U2Z3NpblgxVTRJR3N0aUlhdVVva0dhc0JkRllsS25UZXpsS2UyLVJpbHNFZFJPemtYRXBuMW1qSk9JVUFHbi1RdTNyWnB6NjJsVnhwQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNR05XaGkxeV80T0VJa1k2a0pGZjZPRng1VDZvSkhybExwTEJSYkplazJYekRxa0REYU5mZGxiNkxoYmYtZktFZlJIR2xIdjhBWWNvc052Qm5jNWRKNnJtNGRISWFEVVE1eXVqT2hNV0RNcElVeThFd2ZqMDNBT3hWMGljMnk4ejRxU2tpMEotb3RPaU9nNlBGSDBTX0VMODBaYWVxZV9MS2NOTU02WUpqT0pFb1FvZXEw0gHAAUFVX3lxTE5abzdoWUxaR2lQZWZmR1NGVjYzeXRDbjN3SnFMNWJoX0djWUNCZHF1VS0xTU9STDZaWWZzTEFqdXFRVDYtS3FQc0V3dGp5ZU5uSHByc21YQWloWno0VGI5dkI0a0cwT0tUX2FlRmdZdGJFQnBjQkNFMHRhWTVMeWRBYWVaUGphN25XYUw3bkYwbUF0QU55NC1PYUJ4R1VwSEROSEVYY3hsSFdhWVEyTF9VdVZQbUJscXE4YzRCUTZIOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PF apura extração irregular de calcário e cumpre mandados em investigação - Ponto na Curva</t>
+          <t>PF apura extração irregular de calcário e cumpre mandados em investigação - pontonacurva.com.br</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mosaic e Elicit Plant unem forças para desenvolver tecnologia contra estresse hídrico na canola da América do Norte - Portal do Agronegocio</t>
+          <t>Mosaic e Elicit Plant unem forças para desenvolver tecnologia contra estresse hídrico na canola da América do Norte - portaldoagronegocio.com.br</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dependência externa expõe vulnerabilidade do agro goiano após crise do enxofre, alerta Fecomex - jornalopcao.com.br</t>
+          <t>Dependência externa expõe vulnerabilidade do agro goiano após crise do enxofre, alerta Fecomex - Jornal Opção</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alta dos fertilizantes acende alerta para os custos da safra 2026/27 - Agrolink</t>
+          <t>Alta dos fertilizantes acende alerta para os custos da safra 2026/27 - agrolink.com.br</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Queda da ureia melhora relação de troca e reduz custo dos fertilizantes para a safra 2026/27 - Portal do Agronegocio</t>
+          <t>Queda da ureia melhora relação de troca e reduz custo dos fertilizantes para a safra 2026/27 - portaldoagronegocio.com.br</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 19 - archdaily.com.br</t>
+          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 19 - ArchDaily</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Make ID assina nova campanha publicitária da Mosaic - Portal da Propaganda</t>
+          <t>Make ID assina nova campanha publicitária da Mosaic - portaldapropaganda.com.br</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mosaic transforma inovação agronômica em campanha para aproximar tecnologia do produtor rural - Gazeta da Semana</t>
+          <t>Mosaic transforma inovação agronômica em campanha para aproximar tecnologia do produtor rural - Portal Revista Kdea 360</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxONkRONXYzRFllZmpxU0ZTYnAzc2trWHBXNE9UX2tfRDJETHFZN28tbHRBV3JHZWV6emlqQ0plUWNWNWNTTDRfQWVjX2dScFpjdV9VTU0xb0JxN3RreV9GaVpYdzc1Uk56Z1E5TzRJQlh3cFpWcjF3T2VTdl9Cb1hHX1RXWjEyOGxKR0NsS3JzTTBEbkdJYlRYRlF2SHhoLW5lU1FVRG1hNDJQMG5RaDVDQVBtcHd0V0hQVXhZcWppU0VRYk84aVhZVnVLMFJ0V1B5SUFNWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQelhhdmFxT0ZKRG5MenJyRElINW5HVGVVLVZOVWJJY3RVaXRKeXRTMHZHcHhQeVVZNlY3bXFYa0RiUHFQbWRDVWlJTm5RSmR4R3NVak04Zk40ZHB4cG1oZG9jNzA1d1ByMjVSVWIzWkY5blRvM3F3OGZUR1dsNk1yX2xtVTlHeUxuZ25MUHd1bGxYUWtNcTNoY19TSnAyV1kydXZJblhMSjJGdXZaTWQ2aWhrMk5rYmx2M2ZlRDZGRGtBaS1UdU9ETnI1X2VsZTFfMGlR?oc=5</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mosaic transforma inovação agronômica em campanha para aproximar tecnologia do produtor rural - Portal Revista Kdea 360</t>
+          <t>Mosaic transforma inovação agronômica em campanha para aproximar tecnologia do produtor rural - Gazeta da Semana</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQelhhdmFxT0ZKRG5MenJyRElINW5HVGVVLVZOVWJJY3RVaXRKeXRTMHZHcHhQeVVZNlY3bXFYa0RiUHFQbWRDVWlJTm5RSmR4R3NVak04Zk40ZHB4cG1oZG9jNzA1d1ByMjVSVWIzWkY5blRvM3F3OGZUR1dsNk1yX2xtVTlHeUxuZ25MUHd1bGxYUWtNcTNoY19TSnAyV1kydXZJblhMSjJGdXZaTWQ2aWhrMk5rYmx2M2ZlRDZGRGtBaS1UdU9ETnI1X2VsZTFfMGlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxONkRONXYzRFllZmpxU0ZTYnAzc2trWHBXNE9UX2tfRDJETHFZN28tbHRBV3JHZWV6emlqQ0plUWNWNWNTTDRfQWVjX2dScFpjdV9VTU0xb0JxN3RreV9GaVpYdzc1Uk56Z1E5TzRJQlh3cFpWcjF3T2VTdl9Cb1hHX1RXWjEyOGxKR0NsS3JzTTBEbkdJYlRYRlF2SHhoLW5lU1FVRG1hNDJQMG5RaDVDQVBtcHd0V0hQVXhZcWppU0VRYk84aVhZVnVLMFJ0V1B5SUFNWQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2267,12 +2267,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EuroChem pode paralisar e implementar layoff em Serra do Salitre devido à crise do enxofre - Diário do Comércio</t>
+          <t>Mosaico romano é achado embaixo de solo de fazenda por detector de metal; fotos - Globo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2282,19 +2282,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1FUmpCMjBWeG01TDVyOEZqbWI3Tk83SjVvdjA4ajBzVWtZTTFTZjA2Qi1HU2RMOUtab3dWelVzbjE4dTUtS3NGSEZ6Rms0SDd3T1I0eUpXVmNGaFJHdlFkdW1SZHM2MDZQM2wtZ0xKcnI3a0lCZ01FNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMXd3SmVjREdQMldNX25yX3FHQTY4bHNtVF94WW1GMTlUUkFmYzJCQUdFNUNBVFR2QnFiYnlsMEJ6M01XWVNpdGNOSXdoYzZWU3hwSE9hZWQtZVBQMFlBTldsUGotV2tueWp5akVrdFk5bFM0U1BpdVYyMHM1czlodmVJTUJHNURZQUd6SjVZZnR4cjhNV09uYmhQajBwTDNBNV9icEluQ2FyZm1UYS1Wb2wyblUyOGQwNjFqRmZOR241SGtxME4tTDJnb3NVX212dW9JYzRCVVpINU9CcWhqMVFLZFhlMk5v0gH3AUFVX3lxTE43QllYTzNKVHk0UVFId0R6ZlRSSVpNWGRDU3c1QTJBTFY1LVJHd2RMNDZwSzhIY19rYnJ5T09xMFVDTEZMZW9ZOFBkRnNudnJnWkRXYmN6d0F2ZXFfbFdRNmJmUm1iRnQ4U2lDblEtQWplRHk0VzNYVGxZZ2VZRHlhaWxFSWhXZmZLc0g0UkVuLWh1ZEdkTFFNMVlZellVNWNCZHI0RE5KanlQZi1lSHh3aDM5WHdwRG5IcVpjZkZvWTZpdmd3a0lENi1CT3pKYXlSdElYbTVkem8tV1YyTEEwNkkteTN2YmNQNUp2REwtUmk2Y0htZ1U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mosaico romano é achado embaixo de solo de fazenda por detector de metal; fotos - Globo</t>
+          <t>EuroChem pode paralisar e implementar layoff em Serra do Salitre devido à crise do enxofre - Diário do Comércio</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMXd3SmVjREdQMldNX25yX3FHQTY4bHNtVF94WW1GMTlUUkFmYzJCQUdFNUNBVFR2QnFiYnlsMEJ6M01XWVNpdGNOSXdoYzZWU3hwSE9hZWQtZVBQMFlBTldsUGotV2tueWp5akVrdFk5bFM0U1BpdVYyMHM1czlodmVJTUJHNURZQUd6SjVZZnR4cjhNV09uYmhQajBwTDNBNV9icEluQ2FyZm1UYS1Wb2wyblUyOGQwNjFqRmZOR241SGtxME4tTDJnb3NVX212dW9JYzRCVVpINU9CcWhqMVFLZFhlMk5v0gH3AUFVX3lxTE43QllYTzNKVHk0UVFId0R6ZlRSSVpNWGRDU3c1QTJBTFY1LVJHd2RMNDZwSzhIY19rYnJ5T09xMFVDTEZMZW9ZOFBkRnNudnJnWkRXYmN6d0F2ZXFfbFdRNmJmUm1iRnQ4U2lDblEtQWplRHk0VzNYVGxZZ2VZRHlhaWxFSWhXZmZLc0g0UkVuLWh1ZEdkTFFNMVlZellVNWNCZHI0RE5KanlQZi1lSHh3aDM5WHdwRG5IcVpjZkZvWTZpdmd3a0lENi1CT3pKYXlSdElYbTVkem8tV1YyTEEwNkkteTN2YmNQNUp2REwtUmk2Y0htZ1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1FUmpCMjBWeG01TDVyOEZqbWI3Tk83SjVvdjA4ajBzVWtZTTFTZjA2Qi1HU2RMOUtab3dWelVzbjE4dTUtS3NGSEZ6Rms0SDd3T1I0eUpXVmNGaFJHdlFkdW1SZHM2MDZQM2wtZ0xKcnI3a0lCZ01FNg?oc=5</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ureia cai forte e muda a conta para a próxima safra - Agrolink</t>
+          <t>Ureia cai forte e muda a conta para a próxima safra - agrolink.com.br</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ormuz pressiona fertilizantes: enxofre sobe 322% em um ano, fosfatados perdem demanda e ureia volta a avançar - Money Times</t>
+          <t>EXCLUSIVO | O que está acontecendo na cadeia de valor do enxofre? - Brasil Mineral</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX1FwemdXWEhUWnBFTkt4NkRMQ1p2aU1zVHB6aVJlbkh5WWJrWURlbkVZa0w3ZG9mLWl2VHZjY3gtekJsSWVrellJX29fRGJvMy1YZlotM3VVR3J5a05pc01UcEx1MjNSUkNVUDdieUx3eTR4RU5PdEEzMlYwVnQ5Yzdja0R1QlRnY1A2T0ZlNUFGTzdiRTY4ek50U0RKRDJtZXoyMlJWQTNGeTdwYlBHQVdYclRhVnFSUHIxRl9QXzBrazB2UGVoWGRaZkJ6SXdaaXBkSUJoeFVDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPLWxUWFlOWFBnTG5hcDBndHo0SVNlaWRSWVhnRjl0S0pQTmpsVHZ2NkszYWxMNld3dUdZZmlnX0xCVl9RMDZEeWRUT1FVYk5vRHpzUUZnRVMyVlRlcVRoY2FZbEh2eE9GQndkeHNLWTRYbTlXcUUzbkpVaWxZa1FCcWpzZ290WDY2ZmFpcXlCWW1QUl8zUkV5eTlB?oc=5</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EXCLUSIVO | O que está acontecendo na cadeia de valor do enxofre? - Brasil Mineral</t>
+          <t>Ormuz pressiona fertilizantes: enxofre sobe 322% em um ano, fosfatados perdem demanda e ureia volta a avançar - moneytimes.com.br</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPLWxUWFlOWFBnTG5hcDBndHo0SVNlaWRSWVhnRjl0S0pQTmpsVHZ2NkszYWxMNld3dUdZZmlnX0xCVl9RMDZEeWRUT1FVYk5vRHpzUUZnRVMyVlRlcVRoY2FZbEh2eE9GQndkeHNLWTRYbTlXcUUzbkpVaWxZa1FCcWpzZ290WDY2ZmFpcXlCWW1QUl8zUkV5eTlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX1FwemdXWEhUWnBFTkt4NkRMQ1p2aU1zVHB6aVJlbkh5WWJrWURlbkVZa0w3ZG9mLWl2VHZjY3gtekJsSWVrellJX29fRGJvMy1YZlotM3VVR3J5a05pc01UcEx1MjNSUkNVUDdieUx3eTR4RU5PdEEzMlYwVnQ5Yzdja0R1QlRnY1A2T0ZlNUFGTzdiRTY4ek50U0RKRDJtZXoyMlJWQTNGeTdwYlBHQVdYclRhVnFSUHIxRl9QXzBrazB2UGVoWGRaZkJ6SXdaaXBkSUJoeFVDUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2597,12 +2597,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Carreta com 35 toneladas de calcário tomba em trecho em obras da BR-163, em Coxim - Idest</t>
+          <t>Com guerra no Irã, estoque brasileiro de enxofre pode não alcançar setembro, afirma Ibram - Valor Econômico</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPYjIzcm5KMWZnZEFHaTFJTGVKaTcyU25Ea0RsODRMYndjN1M1eFYzM2lvN2k3dGJGbkxDcTB3STFDMHAwc0toeW9peGNEVmM4UXZlNGRhaGFEMVlTUXliLTBHcGdzM1J2d2ZBV3R1Y2FGYUl4ZmZ5N05XZjg4NWVRd1RES1ctTVpWN0lIX2xwS21uZHhTb0RXSnZkR2JrYld2ZWZUSk9aWnZ0ZHI0eDNRR05oaEJsLW1wcFdHZnd3SDM5dEJLLXM5Q21yaWZUYzhodXZBWHUtQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWHRWcEVlMmJVOEtOTFhYSUFrbkxvNVcxcTBXNXkwb3VFaXJ1NE5yMXNSZ3cxR0RPT1RhbGRLeTZvc3NFUGJHRDh1LTR5TU5YdXN3U0dtdVJTMElMUGlzUHJQeEVMVWhYbGVSa1BzQ2twNkxpZHZ0dUNVSjBBU1VYOTI1Vk9RUThBZ2xtbWJ4UGRBOHhNMk5Sc1M1QkR3Yk1MbHlSNGhvUU1CcjY2ZENpTTY2OW5yaGJra3pqXzc3ajE0SDZ2Vlczdk5weE54bjlsWml6ZWJwYl96QdIB6AFBVV95cUxQVENsWFVQaUIwTTNGaFItb2sxd1BoX2hLZ1cwTlpUYXJFUHVSd1RoUFFnMTFxR0sxTUJ5aHJVcXJyZXZ0NFpOcUEyTVRNOXlkWFA4ZVlyaW9TZ2JELTJpZ3owZ2k2QjE0SFIxS2wwVUxDWHRPb2s1cGNmTWhzWGxsUUxMbGlfcXlYWlFXakVxNWxkMzdGRkg1YUVfa3lnel9WQjFCUktvM1FoaUxBblVod013Y2dsX1ZPNk1Edkdpb3dkZDFmYlBQYmZza3pOQ3ZZRDVRQWlYR2tfSTFaNTJFd19IMGNlUWV3?oc=5</t>
         </is>
       </c>
     </row>
@@ -2641,12 +2641,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Com guerra no Irã, estoque brasileiro de enxofre pode não alcançar setembro, afirma Ibram - Valor Econômico</t>
+          <t>ENERGIA RENOVÁVEL | Mosaic e Casa dos Ventos ampliam parceria para autoprodução - Brasil Mineral</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWHRWcEVlMmJVOEtOTFhYSUFrbkxvNVcxcTBXNXkwb3VFaXJ1NE5yMXNSZ3cxR0RPT1RhbGRLeTZvc3NFUGJHRDh1LTR5TU5YdXN3U0dtdVJTMElMUGlzUHJQeEVMVWhYbGVSa1BzQ2twNkxpZHZ0dUNVSjBBU1VYOTI1Vk9RUThBZ2xtbWJ4UGRBOHhNMk5Sc1M1QkR3Yk1MbHlSNGhvUU1CcjY2ZENpTTY2OW5yaGJra3pqXzc3ajE0SDZ2Vlczdk5weE54bjlsWml6ZWJwYl96QdIB6AFBVV95cUxQVENsWFVQaUIwTTNGaFItb2sxd1BoX2hLZ1cwTlpUYXJFUHVSd1RoUFFnMTFxR0sxTUJ5aHJVcXJyZXZ0NFpOcUEyTVRNOXlkWFA4ZVlyaW9TZ2JELTJpZ3owZ2k2QjE0SFIxS2wwVUxDWHRPb2s1cGNmTWhzWGxsUUxMbGlfcXlYWlFXakVxNWxkMzdGRkg1YUVfa3lnel9WQjFCUktvM1FoaUxBblVod013Y2dsX1ZPNk1Edkdpb3dkZDFmYlBQYmZza3pOQ3ZZRDVRQWlYR2tfSTFaNTJFd19IMGNlUWV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQbmpSeG9HV1FpeGtBbzEzRTNNc0FYWmZrYU4zTXUyNGJLZkVKblBfTS1hQ0JTcFEzWEF1a1h0WkdaYlZVbzduTUFTVlMzSDMwUjB2aVNnai1lT1NqMjJMVTYxN1p2R19iY1RwQnctc1pPZDY2U3hieTlYUlBNbTE1QzkxdUExZnBfeDRFUDdOT3FwbU1PR3hPUW1kWnlqdTZsbXFJ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ENERGIA RENOVÁVEL | Mosaic e Casa dos Ventos ampliam parceria para autoprodução - Brasil Mineral</t>
+          <t>Mosaic transforma inovação agronômica em campanha - Grandes Nomes da Propaganda</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2678,19 +2678,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQbmpSeG9HV1FpeGtBbzEzRTNNc0FYWmZrYU4zTXUyNGJLZkVKblBfTS1hQ0JTcFEzWEF1a1h0WkdaYlZVbzduTUFTVlMzSDMwUjB2aVNnai1lT1NqMjJMVTYxN1p2R19iY1RwQnctc1pPZDY2U3hieTlYUlBNbTE1QzkxdUExZnBfeDRFUDdOT3FwbU1PR3hPUW1kWnlqdTZsbXFJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNVzZGOGtSTEFHU3BnVnl2ZmpCRHUwbVpHSTlZWkJWeTZ5YXo3QTJmaEQ3NXREaWd4dWNzdHVWemNoUjFkZzNOVDNYTkJfMFQxRW9fNjRZMFRQMGNRTnVhTVhMNFBNaDNsOTdvaHhXZVNvSTZmaHVFNXV5bUNQUUlrcllqZ1JCMU44V0wybHVwRGJiUGk4U0lWVDJoZENwVlh2ZThSSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mosaic transforma inovação agronômica em campanha - Grandes Nomes da Propaganda</t>
+          <t>Carreta com 35 toneladas de calcário tomba em trecho em obras da BR-163, em Coxim - Idest</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNVzZGOGtSTEFHU3BnVnl2ZmpCRHUwbVpHSTlZWkJWeTZ5YXo3QTJmaEQ3NXREaWd4dWNzdHVWemNoUjFkZzNOVDNYTkJfMFQxRW9fNjRZMFRQMGNRTnVhTVhMNFBNaDNsOTdvaHhXZVNvSTZmaHVFNXV5bUNQUUlrcllqZ1JCMU44V0wybHVwRGJiUGk4U0lWVDJoZENwVlh2ZThSSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPYjIzcm5KMWZnZEFHaTFJTGVKaTcyU25Ea0RsODRMYndjN1M1eFYzM2lvN2k3dGJGbkxDcTB3STFDMHAwc0toeW9peGNEVmM4UXZlNGRhaGFEMVlTUXliLTBHcGdzM1J2d2ZBV3R1Y2FGYUl4ZmZ5N05XZjg4NWVRd1RES1ctTVpWN0lIX2xwS21uZHhTb0RXSnZkR2JrYld2ZWZUSk9aWnZ0ZHI0eDNRR05oaEJsLW1wcFdHZnd3SDM5dEJLLXM5Q21yaWZUYzhodXZBWHUtQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Fertilizantes: ureia acumula alta de 14% nos portos brasileiros e tensão no Oriente Médio acende alerta para a próxima safra - Portal do Agronegocio</t>
+          <t>Fertilizantes: ureia acumula alta de 14% nos portos brasileiros e tensão no Oriente Médio acende alerta para a próxima safra - portaldoagronegocio.com.br</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ureia sobe pela quarta semana seguida no Brasil - Agrolink</t>
+          <t>Ureia sobe pela quarta semana seguida no Brasil - agrolink.com.br</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Petróleo e ureia aliviam custos no campo gaúcho - Agrolink</t>
+          <t>Petróleo e ureia aliviam custos no campo gaúcho - agrolink.com.br</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2817,12 +2817,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Crise global de enxofre afeta produção de fertilizantes e gera escassez no Brasil - G1</t>
+          <t>Calcário ultrafino melhora microbiologia do solo, diz estudo - Revista Cultivar</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPN1dLWTRLVFhnS0xxU0hTN21GZUd5SF8tWkFVd2pieVVQa2I2VDRhUFp6UWdwRHlQalh4c2h3OXZZekhuTGc1bmJFV01WNkt4eHVySk55SEw1VWR4aHFDcVcyQzlVS2NVdDJDU1lGekRIOG1hUHdZRkxoOWNhNDZWMEJFU3RNcUxEQ1dVLUIwVmdVdnlBMFBGTlFSWi1aUWNGWXplbGVXNVVDdWJfZThTajFjVm9CN05POGJURzR2QmwyQzNsT2l4VFNsb3M3UkRMcWd0TDgwMDRnMVnSAeoBQVVfeXFMTjUzNmZQamdjVlhkNmlETUNqanBRYS1Md2dFb3lWdkhYVFZwR0lYclREOENBR1l4Y3BpS2pPUDlBN1hzY1EzcUJYVkE5a19Ua0FwdDZYeWQ2aS02YXdxTzBsRGFDZzhwbkdHbTVVeVpiOFFpeHZGWTNOd3FnS1Q4Z2lnNkNqSDFKOEZQUnQwLUMxS2g4R0xVakRhaTVjWnFLYXJNLTFnWTZmZlFBRElDd19xRVhTaW9jT2lWc1NsbGxSdnZMckd4ZVE1TjdPWlRfbG1uWTRYZjZ0QzhjSXlSZDA0N1RBSjh3dU13?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQNXhhYnc0VGZFOEdldDFmUm1iNWRKVENuVGIzRmN3VTl4NG1NajlYRDhBUFY4Y2pQbjNzTDJYdWFEU29tYUs0SnJqekprbTNfTU9DRjR0YmkzT0gwQzROZzJhaDQ0U0pKRWxOQ1lESnNaMU12ZUNIbXBWZ1JxV1llVTlDSFlqM0toX1d3bVYzNHpYZmVMUEswUVJGc3VIRFhu?oc=5</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Carreta tomba na BR-163 em Coxim após cair em desnível de obra - Campo Grande News</t>
+          <t>Crise global de enxofre afeta produção de fertilizantes e gera escassez no Brasil - G1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPaUE5blRnSURmR0VxbUswdlBmekxPcm5tV1laaGhLWDNBSmZxOHJiODRmV3RXLTg1VXZJNjI2SzVacFNLWEY5SFVTZm9oQk1iTEt4Q3oxZzFsT3J6c1dSYm55ajBKY0x0TGc4eHo5MUdHcFhQNlZpMHZ6bzhXZ2VuNGFLeWZ1cWZFOTQ1YWRIY2ZUUjA1MENpRWl6NEVETXVmNDVWZVlGQkdvejTSAasBQVVfeXFMTXFxZUJkVTV1YzMzNmRDRTNZaGJqdTdnekRmejhSXy1feXJrRU1QTmtMaXBvUnVsbWtoeDBzNmVSX2VJYmNkQWpTMUt0UElTVlVuZXlpa1VGVnJ0ZnhINFY5c0JFYWNaVGFWQ1ZWMm1JZ1Z3RGZNRVQ1MVRsRjJqWE1PYURzVllVWW4zYXpKbEVwbnJnZkhLSXZ3WnZTNnZxWWFPUlhkUUxCdUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPN1dLWTRLVFhnS0xxU0hTN21GZUd5SF8tWkFVd2pieVVQa2I2VDRhUFp6UWdwRHlQalh4c2h3OXZZekhuTGc1bmJFV01WNkt4eHVySk55SEw1VWR4aHFDcVcyQzlVS2NVdDJDU1lGekRIOG1hUHdZRkxoOWNhNDZWMEJFU3RNcUxEQ1dVLUIwVmdVdnlBMFBGTlFSWi1aUWNGWXplbGVXNVVDdWJfZThTajFjVm9CN05POGJURzR2QmwyQzNsT2l4VFNsb3M3UkRMcWd0TDgwMDRnMVnSAeoBQVVfeXFMTjUzNmZQamdjVlhkNmlETUNqanBRYS1Md2dFb3lWdkhYVFZwR0lYclREOENBR1l4Y3BpS2pPUDlBN1hzY1EzcUJYVkE5a19Ua0FwdDZYeWQ2aS02YXdxTzBsRGFDZzhwbkdHbTVVeVpiOFFpeHZGWTNOd3FnS1Q4Z2lnNkNqSDFKOEZQUnQwLUMxS2g4R0xVakRhaTVjWnFLYXJNLTFnWTZmZlFBRElDd19xRVhTaW9jT2lWc1NsbGxSdnZMckd4ZVE1TjdPWlRfbG1uWTRYZjZ0QzhjSXlSZDA0N1RBSjh3dU13?oc=5</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Calcário ultrafino melhora microbiologia do solo, diz estudo - Revista Cultivar</t>
+          <t>Carreta tomba na BR-163 em Coxim após cair em desnível de obra - campograndenews.com.br</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQNXhhYnc0VGZFOEdldDFmUm1iNWRKVENuVGIzRmN3VTl4NG1NajlYRDhBUFY4Y2pQbjNzTDJYdWFEU29tYUs0SnJqekprbTNfTU9DRjR0YmkzT0gwQzROZzJhaDQ0U0pKRWxOQ1lESnNaMU12ZUNIbXBWZ1JxV1llVTlDSFlqM0toX1d3bVYzNHpYZmVMUEswUVJGc3VIRFhu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPaUE5blRnSURmR0VxbUswdlBmekxPcm5tV1laaGhLWDNBSmZxOHJiODRmV3RXLTg1VXZJNjI2SzVacFNLWEY5SFVTZm9oQk1iTEt4Q3oxZzFsT3J6c1dSYm55ajBKY0x0TGc4eHo5MUdHcFhQNlZpMHZ6bzhXZ2VuNGFLeWZ1cWZFOTQ1YWRIY2ZUUjA1MENpRWl6NEVETXVmNDVWZVlGQkdvejTSAasBQVVfeXFMTXFxZUJkVTV1YzMzNmRDRTNZaGJqdTdnekRmejhSXy1feXJrRU1QTmtMaXBvUnVsbWtoeDBzNmVSX2VJYmNkQWpTMUt0UElTVlVuZXlpa1VGVnJ0ZnhINFY5c0JFYWNaVGFWQ1ZWMm1JZ1Z3RGZNRVQ1MVRsRjJqWE1PYURzVllVWW4zYXpKbEVwbnJnZkhLSXZ3WnZTNnZxWWFPUlhkUUxCdUtr?oc=5</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Esta bateria pode armazenar muito mais energia que os modelos atuais, e o segredo está em um resíduo industrial abundante que cientistas brasileiros tentam tornar mais estável - Revista Fórum</t>
+          <t>Estudos sobre materiais para baterias de enxofre abrem possibilidades de otimização da tecnologia - Agência FAPESP</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE9wcWZqWXBIRHEyV1B2Qi1FREUzVGtuTUdoT0RrZDF0X0VrN0RjVjB1ZjZMVmJpSDAxSEZBbHlJYlhuMDVIbnlHQWw0TTdsb2RFY3pXOF9GSmNvZ1VOMVVGLXZnRGtEWFVVY0d0aFAweWNZbHFLWnp0V0lR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSnVhNTZSSGVGTmx0dUtpeXBqaXFOWkw2UGQ5bll0S2EyWEVwa3dObWE1am1rc3pGNHhQdWhPdEFGNHR3Y1dTalFKU2hCa19QU21iTDdXRnF2c1ZqSUplTF9ZY282M3RWb2pOSExQbDI5cmxmbmtZdEM3bUp3azlmR2RoNWFzNjRPYXdMUTJSaG1RRy15OVd2dGpBZlU1bnBGZHJ0LVNBcGFfWlBwcVpDY2hLOFp0Sk02SjBZZ2ZWYUhZT09sRElrVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Estudos sobre materiais para baterias de enxofre abrem possibilidades de otimização da tecnologia - Agência FAPESP</t>
+          <t>Esta bateria pode armazenar muito mais energia que os modelos atuais, e o segredo está em um resíduo industrial abundante que cientistas brasileiros tentam tornar mais estável - revistaforum.com.br</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSnVhNTZSSGVGTmx0dUtpeXBqaXFOWkw2UGQ5bll0S2EyWEVwa3dObWE1am1rc3pGNHhQdWhPdEFGNHR3Y1dTalFKU2hCa19QU21iTDdXRnF2c1ZqSUplTF9ZY282M3RWb2pOSExQbDI5cmxmbmtZdEM3bUp3azlmR2RoNWFzNjRPYXdMUTJSaG1RRy15OVd2dGpBZlU1bnBGZHJ0LVNBcGFfWlBwcVpDY2hLOFp0Sk02SjBZZ2ZWYUhZT09sRElrVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE9wcWZqWXBIRHEyV1B2Qi1FREUzVGtuTUdoT0RrZDF0X0VrN0RjVjB1ZjZMVmJpSDAxSEZBbHlJYlhuMDVIbnlHQWw0TTdsb2RFY3pXOF9GSmNvZ1VOMVVGLXZnRGtEWFVVY0d0aFAweWNZbHFLWnp0V0lR?oc=5</t>
         </is>
       </c>
     </row>
@@ -3147,12 +3147,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Relação de preço da ureia e do milho no 1° semestre, entre 2018 e 2026 - Farmnews</t>
+          <t>Escassez global de enxofre paralisa indústria de fertilizantes em Goiás e ameaça mais de 600 empregos - G1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3162,19 +3162,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPWlBYQkw2bl9fd3JLcG8wN3FvUkhLSHNYY1d6Um5COVM5RjNDUUZNSndYRzVQU2NXY3RodVl5bWx6aHRVcm0xeHEtWUx2SGNPYWZUYkgzVnR1akc0U1RXV3NMYmJYOERrQnhkLUYydW5RUkY4c1V5T0pOdzdldWZQZ1lNTk1iekVCTHJUUVlTbFd3dGgyUzFVR0ZBaXNpUmdabDhJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQazVGaElwb0d2SFd0bjRwZE9yM2E3VEt3UzVZaV9TRUUtNGtsQ2tTS21jbVRNdXk0M3ZQd3Vhc3BtakpoN2JOZEh0UllpNFNNU1RBQVZLb0otVnN0cnRUMHNROTFVYWNzMDJ4bmNIbjhsaGhZZVFDcFllcV9oZ3dFa25HaWdtdDJWQ01jeEllTnRYYi0zMFhfMEJ3ekRuNl8xOTlUN2dWbGdkX1p3NnQ1N2FHbFRUWjJSUlNla3lTSFpFSlV6U2w3QVlrNW1OVm5HVjVtQllSaTN0d3ptWjdObnVSWUY2bDRWUGltadIB-wFBVV95cUxPallYVTZnVk1ndHB4SGlqWGVwUWxla2RjRlh3SWtrMy1hWFU4Zkk3czd0ejhral9ha3FKV3Y5Mk9YNDBmejdTVXc0eDZRdGdORDRENFRIZjdkQzhLTUl0Sl80Z1dRQm9HdGlRTGxDT19xTTV1OVZrbHlGWGV1ZUpEaEh6Z055NHZlTS1vblFhVWJuNm5VWGE2WE5KNElrdGJTbEdMSnJVWTVrMUNrNGE1NU9QaVAwRkwxYUtvMFh4Mm4wRzVPay1EdnVTUjZhV1J1Si1KSHYwYm9DcGVVdmZ1OHZNM3hicWttR21GV3BscHp6VlBpd2ljRTJZaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Escassez global de enxofre paralisa indústria de fertilizantes em Goiás e ameaça mais de 600 empregos - G1</t>
+          <t>Relação de preço da ureia e do milho no 1° semestre, entre 2018 e 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQazVGaElwb0d2SFd0bjRwZE9yM2E3VEt3UzVZaV9TRUUtNGtsQ2tTS21jbVRNdXk0M3ZQd3Vhc3BtakpoN2JOZEh0UllpNFNNU1RBQVZLb0otVnN0cnRUMHNROTFVYWNzMDJ4bmNIbjhsaGhZZVFDcFllcV9oZ3dFa25HaWdtdDJWQ01jeEllTnRYYi0zMFhfMEJ3ekRuNl8xOTlUN2dWbGdkX1p3NnQ1N2FHbFRUWjJSUlNla3lTSFpFSlV6U2w3QVlrNW1OVm5HVjVtQllSaTN0d3ptWjdObnVSWUY2bDRWUGltadIB-wFBVV95cUxPallYVTZnVk1ndHB4SGlqWGVwUWxla2RjRlh3SWtrMy1hWFU4Zkk3czd0ejhral9ha3FKV3Y5Mk9YNDBmejdTVXc0eDZRdGdORDRENFRIZjdkQzhLTUl0Sl80Z1dRQm9HdGlRTGxDT19xTTV1OVZrbHlGWGV1ZUpEaEh6Z055NHZlTS1vblFhVWJuNm5VWGE2WE5KNElrdGJTbEdMSnJVWTVrMUNrNGE1NU9QaVAwRkwxYUtvMFh4Mm4wRzVPay1EdnVTUjZhV1J1Si1KSHYwYm9DcGVVdmZ1OHZNM3hicWttR21GV3BscHp6VlBpd2ljRTJZaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPWlBYQkw2bl9fd3JLcG8wN3FvUkhLSHNYY1d6Um5COVM5RjNDUUZNSndYRzVQU2NXY3RodVl5bWx6aHRVcm0xeHEtWUx2SGNPYWZUYkgzVnR1akc0U1RXV3NMYmJYOERrQnhkLUYydW5RUkY4c1V5T0pOdzdldWZQZ1lNTk1iekVCTHJUUVlTbFd3dGgyUzFVR0ZBaXNpUmdabDhJ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ureia valoriza mais de 18% em um mês puxada por demanda e geopolítica - CNN Brasil</t>
+          <t>Pampa Energia anuncia investimentos de 2,7 Bilhões em fábrica de ureia na argentina - GlobalFert</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQMGtJYlMwLWUzVkNubGpBZjAzUTNhY1lUWjN0aHd2ZGxVLUxRS0NmbDZIRXJzRFk2VnFCaUVrVFlodHdYSmJzVWZjelV1WFJhVGZOdXVzN083N2xVb24wakFhTjRWUWw5ZGRTeG5PNkt1MVo3T0VNbGxxVUliVUtvRDBaYU1zZU1Rc2VnbHFudUJMaFk4eExyNUhqV0stdXkxRFE3WC1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOcVVHZE43T3MwdHc2RUc0dWl0T3ExNFNMcGFraTJkeXRJZElYUzZmOXkwSkt5d09oRm92Y1BzU1VzdmN4bFBjRFVTUnRVU1BRTks2emRvWXh1Qm9VaDdTSVFNV2p5TWNpaXZaZVlmRFZCYXF2c0YxZFU3blhrVVB5VUxHOVdkbkl0Q0lVak1MeHRjWjdDeVlCc0Fwd3IyakgwczdXczFLRmRDNUJPR2p3bHRjSlBPd1VTVHZWMGxaNWRTTktoWGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Pampa Energia anuncia investimentos de 2,7 Bilhões em fábrica de ureia na argentina - GlobalFert</t>
+          <t>Ureia valoriza mais de 18% em um mês puxada por demanda e geopolítica - CNN Brasil</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3294,19 +3294,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOcVVHZE43T3MwdHc2RUc0dWl0T3ExNFNMcGFraTJkeXRJZElYUzZmOXkwSkt5d09oRm92Y1BzU1VzdmN4bFBjRFVTUnRVU1BRTks2emRvWXh1Qm9VaDdTSVFNV2p5TWNpaXZaZVlmRFZCYXF2c0YxZFU3blhrVVB5VUxHOVdkbkl0Q0lVak1MeHRjWjdDeVlCc0Fwd3IyakgwczdXczFLRmRDNUJPR2p3bHRjSlBPd1VTVHZWMGxaNWRTTktoWGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQMGtJYlMwLWUzVkNubGpBZjAzUTNhY1lUWjN0aHd2ZGxVLUxRS0NmbDZIRXJzRFk2VnFCaUVrVFlodHdYSmJzVWZjelV1WFJhVGZOdXVzN083N2xVb24wakFhTjRWUWw5ZGRTeG5PNkt1MVo3T0VNbGxxVUliVUtvRDBaYU1zZU1Rc2VnbHFudUJMaFk4eExyNUhqV0stdXkxRFE3WC1B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Basalto substitui calcário e corta emissões de CO2 no cimento Portland - newenergybrasil.com.br</t>
+          <t>Da guerra no Oriente Médio à Mosaic: entenda por que empregos estão em risco em Uberaba - jmonline.com.br</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3316,19 +3316,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPRUR3TU5Fa0QyVmFzZWdfZlU3TWtlOURGS0hZMW5DcS1McDI3emdKbk9ZMUhBUmt2RmcxRXM2ejd6SEVPMC1SRXR2cV91Ry05NmFvbEhza25qRFdtdlh1VjNaSGxfMGFWRUZSSENkYnBYNmMweWp1V0s3TTRnUF9fcll1ZkRpT1RYYkhwS0tzU0tHRjZJbDV0dUY2XzVYMzlGaVdGYzRMZjJGMnRlRjVoaUlObVlDQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNbHZvTzRTZHlrTHpsQmFFV0k2Qi0wWTh1SXhHN0pvcDgwUzVHRGFVVzc4bXNSeHJLRGlwQzkzRWxtYVJERFBReVlRaC1paTNIRHN0YWVhc0QxQnJyaXBrdzhqeWdtSzZ6Vk1jaU9SZ0VNMkc3UHg0YlRVdmtFNVZWT0tybTdRUm9STWt4SlBKM0ktLXZ2SVRtb3ZYaC1ZV2VSQ0NqMWoyVmROQUVBNDNyazNmLTFvc3l3M2JzWDlKUHlaUmdM0gHMAUFVX3lxTE1qQkF4YVY1VXNFRjdHSllUaTJOM0c2V3V4Y1dYYWJyWmFDOXlJWXZVaEd1MWxhS185REZyc3owaHA5NjlrSzNSdC0wc3hzOXBkQ2xrMnRPcFZ6ZUFHYXlxcDQ4eUxBSU12Z2luVVNFRVMyRGx6SnJxeXVwQmhKT0FSODNWZVVPekNqVlM4aUVWSE5iTHRiRHl6RklWMkRGTXQzVW5YN1VBS0YtUERfeWlLX3hsNk1nZGJUc3diRTBqZ3ZLWmNjMWpKNWkxQw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Com “brisa de otimismo”, mercado de fertilizantes reage, mas ainda corre contra o tempo - AgFeed</t>
+          <t>Basalto substitui calcário e corta emissões de CO2 no cimento Portland - newenergybrasil.com.br</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPVVh2bHF6bEVibGowdkxud1piX1FVWEpHWTVpLXNWUW80eU92UXVUdElvOFlJMEVRaDcwckhLZmtQcmJnOElrU1RlSEhKeEZzRjRzRmJHZW1Cb3BqOG9KR2FoeTZQNVM1b1l4aUZvVmhCeTBfQ2Q1ZndnbEFOLUkwQ1YwYXd3ZGw0cExzR2w5bVNsNG9zODh1bkVad2pZdFpodmdEbFVIcGtYSnlHLTU2S1hQem92QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPRUR3TU5Fa0QyVmFzZWdfZlU3TWtlOURGS0hZMW5DcS1McDI3emdKbk9ZMUhBUmt2RmcxRXM2ejd6SEVPMC1SRXR2cV91Ry05NmFvbEhza25qRFdtdlh1VjNaSGxfMGFWRUZSSENkYnBYNmMweWp1V0s3TTRnUF9fcll1ZkRpT1RYYkhwS0tzU0tHRjZJbDV0dUY2XzVYMzlGaVdGYzRMZjJGMnRlRjVoaUlObVlDQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Da guerra no Oriente Médio à Mosaic: entenda por que empregos estão em risco em Uberaba - JM Online</t>
+          <t>Mosaic paralisa produção em Catalão por falta de enxofre e sindicato teme impacto em 650 empregos - Diário de Goiás</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3382,29 +3382,29 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNbHZvTzRTZHlrTHpsQmFFV0k2Qi0wWTh1SXhHN0pvcDgwUzVHRGFVVzc4bXNSeHJLRGlwQzkzRWxtYVJERFBReVlRaC1paTNIRHN0YWVhc0QxQnJyaXBrdzhqeWdtSzZ6Vk1jaU9SZ0VNMkc3UHg0YlRVdmtFNVZWT0tybTdRUm9STWt4SlBKM0ktLXZ2SVRtb3ZYaC1ZV2VSQ0NqMWoyVmROQUVBNDNyazNmLTFvc3l3M2JzWDlKUHlaUmdM0gHMAUFVX3lxTE1qQkF4YVY1VXNFRjdHSllUaTJOM0c2V3V4Y1dYYWJyWmFDOXlJWXZVaEd1MWxhS185REZyc3owaHA5NjlrSzNSdC0wc3hzOXBkQ2xrMnRPcFZ6ZUFHYXlxcDQ4eUxBSU12Z2luVVNFRVMyRGx6SnJxeXVwQmhKT0FSODNWZVVPekNqVlM4aUVWSE5iTHRiRHl6RklWMkRGTXQzVW5YN1VBS0YtUERfeWlLX3hsNk1nZGJUc3diRTBqZ3ZLWmNjMWpKNWkxQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNend4a0d3ZVRsdjhtTWlXRWhJQTBlSXFEdjNYX1ZpcElMY0FiUzUySmM1dzQ3TmJwOHhYeGF1eE1jYXYyUXhvWVVOUDdoT05keEg3QmFZbHpzZVByVG4zLV9VZnVHNlYyTHhUUTVoVFB2UlNQWHVXNElsV2N1MjRlVUxLNVhadGRucjB4LURtdXJWSHRPem1QYmFDNVVrNXFTMUFuNkdlMVhyU3pLRmFUV2VvYU1YVWpZLTVMY2pHNDlKTTJXTE81YmtfdVlHVDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ergueram pilares de calcário de até 5,5 metros há 11.500 anos, quando a agricultura ainda começava a transformar a vida humana - Revista Oeste</t>
+          <t>Com “brisa de otimismo”, mercado de fertilizantes reage, mas ainda corre contra o tempo - AgFeed</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>19/07/2026 04:00</t>
+          <t>20/07/2026 04:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQMHFxcXZoN2VHVEtqVWMtMXR0Tm5RX2dqZnJsT21XZUJnRW1qX0h2dUxoNzcyUUZGQ2ZvY1Fzd0lsTlk3MDdVMnBTSk5jbGJfY2VRSGFScnoyS0dybGlpME1odk9ZdGJSV3lNUkN5VUItTHZUdGVObFV2R01UbzZGUXRMUl9iMVB1LUh4X2JTZU9fSjA5aW04bHI5YldvT1Q1NFpsZFkyRGRQQTgzVko4elVBODRsbWhTeXdpVFRjX195WTE5NVFOclNBV0VOSmVLRG5IZlk2NWtuMEFkVTMzYVB2aHBwb2NpTkw1dGxWbkdLa2loekxXS0J4NjBMemhSUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPVVh2bHF6bEVibGowdkxud1piX1FVWEpHWTVpLXNWUW80eU92UXVUdElvOFlJMEVRaDcwckhLZmtQcmJnOElrU1RlSEhKeEZzRjRzRmJHZW1Cb3BqOG9KR2FoeTZQNVM1b1l4aUZvVmhCeTBfQ2Q1ZndnbEFOLUkwQ1YwYXd3ZGw0cExzR2w5bVNsNG9zODh1bkVad2pZdFpodmdEbFVIcGtYSnlHLTU2S1hQem92QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3416,61 +3416,61 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Na China, um sumidouro de 192 metros esconde árvores de 40 metros e três cavernas sob uma paisagem de calcário - Revista Oeste</t>
+          <t>Ergueram pilares de calcário de até 5,5 metros há 11.500 anos, quando a agricultura ainda começava a transformar a vida humana - Revista Oeste</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>18/07/2026 04:00</t>
+          <t>19/07/2026 04:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOaXc5OTRzUXRXT1o0cFpOZE9jbnoyVUpVTzZ6QzBaaFZVNVZfbDJ0YnA5RHNTdmFrMmlTUWNGbHNqQ1ZoY0hpZE53U3EyVEJQU2RDMUtzYUs0c0Q3aG9FTl9RaWlFVUY0cjA5RlFPZGM4anVmeDRYdlhQQ05WRnZNNXFsQ2x1eGxfcU1sS0F6X0RCRjVHOWhwYWZQdUdGN2tQQWF0QU9xZnAxM3JqQjFYUUtILVRaSW8yQlMwQVBRa3VCWWFBdWVrc0dURTY0OUhydGt2WUs5Y3NkRjhjUWVidzVKVGVsaTRlY0VyVS1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQMHFxcXZoN2VHVEtqVWMtMXR0Tm5RX2dqZnJsT21XZUJnRW1qX0h2dUxoNzcyUUZGQ2ZvY1Fzd0lsTlk3MDdVMnBTSk5jbGJfY2VRSGFScnoyS0dybGlpME1odk9ZdGJSV3lNUkN5VUItTHZUdGVObFV2R01UbzZGUXRMUl9iMVB1LUh4X2JTZU9fSjA5aW04bHI5YldvT1Q1NFpsZFkyRGRQQTgzVko4elVBODRsbWhTeXdpVFRjX195WTE5NVFOclNBV0VOSmVLRG5IZlk2NWtuMEFkVTMzYVB2aHBwb2NpTkw1dGxWbkdLa2loekxXS0J4NjBMemhSUkE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 7 - ArchDaily</t>
+          <t>Na China, um sumidouro de 192 metros esconde árvores de 40 metros e três cavernas sob uma paisagem de calcário - Revista Oeste</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>18/07/2026 01:44</t>
+          <t>18/07/2026 04:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPZVRlQ1V1aUlpcmFSQ0ZIOWU3S1JSM2xNWDhwazQ3cmx1MHQ4aWt2dFc4a1pNbmNDNWJCUkR4RXZ1T1NEYkRpVVpkN3pyRnVXdmNZejhyRmtJcTFROTYtQjRqYnBkSkZ3ODBFSlNFVngtOXNqTDJBYmt5Si10YmVUT01pdWtNSFkwR3RYZVJ1TTk0X2ljeXRMRW1nVGgwTjNNYUUzeFdXR3p5NEc3Sk9pbHBMREl3eV8yZVlDc0dIdXBRVjRTQUtyZ2tsa3FXZDdsZW45NDFOOVBMOXdkakFKYklRdDlUWmtRUTNVMnY3R3NQNTZkRFE1N1VDRWRrRWNoQ1Q2T2ln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOaXc5OTRzUXRXT1o0cFpOZE9jbnoyVUpVTzZ6QzBaaFZVNVZfbDJ0YnA5RHNTdmFrMmlTUWNGbHNqQ1ZoY0hpZE53U3EyVEJQU2RDMUtzYUs0c0Q3aG9FTl9RaWlFVUY0cjA5RlFPZGM4anVmeDRYdlhQQ05WRnZNNXFsQ2x1eGxfcU1sS0F6X0RCRjVHOWhwYWZQdUdGN2tQQWF0QU9xZnAxM3JqQjFYUUtILVRaSW8yQlMwQVBRa3VCWWFBdWVrc0dURTY0OUhydGt2WUs5Y3NkRjhjUWVidzVKVGVsaTRlY0VyVS1R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Melhora no poder de compra de fertilizantes - GlobalFert</t>
+          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 13 - ArchDaily</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>17/07/2026 20:47</t>
+          <t>18/07/2026 01:44</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNY0VhZGVublZBbnlpeHVObmRmeXV0dzlUT0FwXzZBSzNqUWh5U3FqMThXOXY0UW81X09wanNPWk9FVk4tU2lhcmFwQWdtR1FYTjk4eG1SdE9XM3NFWkxTRGRjcGJ2RVdpcm9NMTRXTUlGazdWbkJydWVsUXgwWTZOcGNFQUhBQ0haTzRFOEJTSml2U1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxQaFpaYnh2bVFhN3B6MTZ1dEpmT085TUFMSUVmSEF4TnBRM3Z4X2lXWDN0U3dVZlY4bUNRVDgtQXo5RDBUTV83NWFfa3RFMHBvMHk4ZlI4aWloN2txbVVuaGFpVzViNmRGbEhnaTlvVzg5VkhfaXZoRTBzQzhaeld0V2VMSTN0QjV6dlYxbDB6QlFfUTZxNnRSNHFRTldwcXN2dTUzVk9iX1Q0RENkbjhRLUt2NHFydHNCR21EcUZHWEFqRk9fMjRCSDFJR3hMajk0UWxGZ3prQUdXVEVtQVFMYk11N2VmQXpIX0VuOTkzYkVLV29DLW1ObUVuRnlReGxiRkFXZ3d3?oc=5</t>
         </is>
       </c>
     </row>
@@ -3482,105 +3482,105 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Bolsa de qualificação pode evitar demissões na Mosaic - JM Online</t>
+          <t>Melhora no poder de compra de fertilizantes - GlobalFert</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>17/07/2026 20:39</t>
+          <t>17/07/2026 20:47</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNY0VhZGVublZBbnlpeHVObmRmeXV0dzlUT0FwXzZBSzNqUWh5U3FqMThXOXY0UW81X09wanNPWk9FVk4tU2lhcmFwQWdtR1FYTjk4eG1SdE9XM3NFWkxTRGRjcGJ2RVdpcm9NMTRXTUlGazdWbkJydWVsUXgwWTZOcGNFQUhBQ0haTzRFOEJTSml2U1U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Índia aprova nova política de investimentos em ureia - GlobalFert</t>
+          <t>Bolsa de qualificação pode evitar demissões na Mosaic - jmonline.com.br</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>16/07/2026 20:53</t>
+          <t>17/07/2026 20:39</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeUZvQlZWVTlrTnNwbkkwZnVGT3hZYlNEWjhCeEVxR21OOU5aV2YwdmoxUHV4X0Yycm1LSGlHYkp3S1F5NkRaZFUyTEpBdmNaemJhSFB0WXFYNmU1c194SFZtaXBlQlF5d2Z3a0ltOThHbXVNSGxvLXdXT2JfT2hkZUs3ZHF0MUFodzJPdW5WSzVlQk1rZzlyNGZuNmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 8 - ArchDaily</t>
+          <t>Índia aprova nova política de investimentos em ureia - GlobalFert</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>16/07/2026 13:21</t>
+          <t>16/07/2026 20:53</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNQlJkVjBpYk1xQ090TG90alp1VElrclpxYW9QVGg5MEVCYXBGb01nMzNzQWY1XzZmRWZDVnplTVVFZkpKVURwUEtfNFlLc2VnX3lNVEZoekZCNVB2WnUxTUZmMUNJLTVSQU1CMlBWX2dWZkNMS0RDMnhXVVJCT1BSYkhUeHJyRFFyb01sY0daYl9LckVFc1d6T24zQnkteHBpb1VvYTh3ajBXQUIxWk1TQUlIel9ldUpkLUFudQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeUZvQlZWVTlrTnNwbkkwZnVGT3hZYlNEWjhCeEVxR21OOU5aV2YwdmoxUHV4X0Yycm1LSGlHYkp3S1F5NkRaZFUyTEpBdmNaemJhSFB0WXFYNmU1c194SFZtaXBlQlF5d2Z3a0ltOThHbXVNSGxvLXdXT2JfT2hkZUs3ZHF0MUFodzJPdW5WSzVlQk1rZzlyNGZuNmY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>São José: inscrições abertas para programa de transporte de calcário - PortalR3</t>
+          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 8 - ArchDaily</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>16/07/2026 07:46</t>
+          <t>16/07/2026 13:21</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPVG5tTDNLd2owRzFfRWszRVRWNzJXUXd6S0dHdEp4Z1EtLV8xSmhzV0wyaHFKUnduUnZLRVo1UHViSkUyNi1lbU9TWUpXT3d1Q0Jwdjg3eWg4cXVWSXFFR0VZdDZpUnV4RnYwTzRIVW5ielUtdFloRnVHQnpoclVqM29TbnJYYV9lQnRLT3lVcHpxbl9OMkFPWXU2LUF1T0t2Y0I5RHA0SWNjdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNQlJkVjBpYk1xQ090TG90alp1VElrclpxYW9QVGg5MEVCYXBGb01nMzNzQWY1XzZmRWZDVnplTVVFZkpKVURwUEtfNFlLc2VnX3lNVEZoekZCNVB2WnUxTUZmMUNJLTVSQU1CMlBWX2dWZkNMS0RDMnhXVVJCT1BSYkhUeHJyRFFyb01sY0daYl9LckVFc1d6T24zQnkteHBpb1VvYTh3ajBXQUIxWk1TQUlIel9ldUpkLUFudQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
+          <t>São José: inscrições abertas para programa de transporte de calcário - PortalR3</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>16/07/2026 04:00</t>
+          <t>16/07/2026 07:46</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNXZMb055LVlJVzBzMmRkX2xrNUNpZHREU0NjUGUxR2wtNmU1a3RNaEZNdzVMd2lzaDUwMDNjanpZbjVLck9wX2RmdFk0UnNvWGJtdjFLcEtrUVdjNm14MXR1N1U0RWdyUTNjNWsySm5DUjBnWHFXUWJxNGloMmlmbkpRQWlCbW9RLTRzSkdxcGxUZjJCVTBfVldOV0xOQllmTGVrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPVG5tTDNLd2owRzFfRWszRVRWNzJXUXd6S0dHdEp4Z1EtLV8xSmhzV0wyaHFKUnduUnZLRVo1UHViSkUyNi1lbU9TWUpXT3d1Q0Jwdjg3eWg4cXVWSXFFR0VZdDZpUnV4RnYwTzRIVW5ielUtdFloRnVHQnpoclVqM29TbnJYYV9lQnRLT3lVcHpxbl9OMkFPWXU2LUF1T0t2Y0I5RHA0SWNjdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3592,73 +3592,73 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado ‘Casa de Mãe’, da marca Qualicoco, por excesso de enxofre - Estadão</t>
+          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>14/07/2026 15:20</t>
+          <t>16/07/2026 04:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPYlAteXhKQmc0VXRFcE5jcWZGbkxlZzVJRXd2V3FiWHN3VkJfU2J3cFVZZVFRQ1dvSXZ4VE1VY0FjbS1EanN1c1ZXa1lMLU84RGx6cG1TTHdJNHR1UDEwYnZoV2pMREFmd3V5V0UyY3BuLVBQMnVNUEtqb0tFTGpKT0Z1S0RJeU5RZ1VFdF8tbXdPNTdMVFlQQzBVMldOZ3FOa3RRa053QXc4ZXNWWlcyWFk1YmI1a3lsVkFrZ1JDSFZKU1hMOHpENjltVUZrWUFYT1dEWGl6S2JKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNXZMb055LVlJVzBzMmRkX2xrNUNpZHREU0NjUGUxR2wtNmU1a3RNaEZNdzVMd2lzaDUwMDNjanpZbjVLck9wX2RmdFk0UnNvWGJtdjFLcEtrUVdjNm14MXR1N1U0RWdyUTNjNWsySm5DUjBnWHFXUWJxNGloMmlmbkpRQWlCbW9RLTRzSkdxcGxUZjJCVTBfVldOV0xOQllmTGVrMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - G1</t>
+          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir 'cheiro de enxofre' - UOL</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>14/07/2026 04:00</t>
+          <t>15/07/2026 04:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUZhRXRNY2trQVZ1YkFrZTVzNEdyX0xBSkZOdGduN080THhRLWNrRzNRV2piY1hPSkNOaDZxcWh0a2NnNzZOR2hGeHR4Rkh2QjdVNDlDdXhlcFhlRVB5R0JEUHp4c1lhRFh6bmdJdWlRU1h1WEhkQ2VONEhrUWZBVnRJRl81SE1sN0Z3dGx6dGxTd2NDUzYxM01oVHdKTVRVMDlXZXMxZmF0SnFrTjNPUjZtZlRtamVwTmZxaG1SLWtMYWxaa1E3OEVFTlBkQkRQb2ZIQ1AtSkdPVXRwQUN4aHBtdmZXVnNQYUtydUxzeXTSAf8BQVVfeXFMUEtWemJJN0VvVFA5R2c0WE43dWdwQW1qaXZBMGZzdUlzVWc3NXI1LWE1cE9ZT05Fb2JRbVAxdUdVSHZhWVpwa2VDU0NVbFBSNHVZZnNFZVdQN0loOVlUeUtKMll4d2xLclh3dXhTYVZSM3dHNXBSWXNMUGhydEcwYU1Lc1B5RHU4cEpQclFNNEZMZXZjeUp6QjVCc3l2anp4Ymw0M0VmNU9kQ2hlaUMtZ1c4VTg5eWF2eXhoMXh0UERTSUdORlcwQ0hCUDZTd21GUEdVYVM4aEFVTi1mWUxzbVZyUnhQdGhfcF9wdmxzSUtDYmh1dGVqX0pFa1g2QnFV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPTkxyWkdnWjVncmNISHdDSW82bTRtVzQtWUtTdXhENjJpczl4anRSR2htWklCMm1VTVZ6TU5BeTZNQ2UySV9pd3JBdkNXbkZGUnBPYUNkcWttZHNOTk9Xbmo2eVBJZVZXU3ZNcVd4S013a2Y5MjB4eDdYWXcyUFlVNGY0Y2ZGckVhLUltX283Z1lsbjBtbzVkVEJlVk5XSzdXLVl1SmFla3VXRWJtUE8tY2JFTUlTYzBBcktJV2Zra01PNVhneDZwQkVNQW9TNHRyZGE5bUdrVkNLNmQxUHBV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
+          <t>Anvisa manda recolher lote de coco ralado ‘Casa de Mãe’, da marca Qualicoco, por excesso de enxofre - Estadão</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>14/07/2026 04:00</t>
+          <t>14/07/2026 15:20</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPYlAteXhKQmc0VXRFcE5jcWZGbkxlZzVJRXd2V3FiWHN3VkJfU2J3cFVZZVFRQ1dvSXZ4VE1VY0FjbS1EanN1c1ZXa1lMLU84RGx6cG1TTHdJNHR1UDEwYnZoV2pMREFmd3V5V0UyY3BuLVBQMnVNUEtqb0tFTGpKT0Z1S0RJeU5RZ1VFdF8tbXdPNTdMVFlQQzBVMldOZ3FOa3RRa053QXc4ZXNWWlcyWFk1YmI1a3lsVkFrZ1JDSFZKU1hMOHpENjltVUZrWUFYT1dEWGl6S2JKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Tensão em Ormuz afeta produção de fertilizantes no Brasil - CNN Brasil</t>
+          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - G1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3668,95 +3668,95 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaU1rV2NIc09fUTUwZVc4TEI3NEhSZ19UcHVqdEJKaDJ5dDNqSDdUaGo2VXlpWUp6OEpoRnU4ZEpCb2MxQ1RURXV3S3dreU1Lc24tVk8wazB0OTBsN2RIMmVER0ROd2hxUE1QOEdPMFZkc01MQVlHcWdDNDN1dVNETzFQQV94cDFwV0VzeGozdldYbXBBMkQ0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUZhRXRNY2trQVZ1YkFrZTVzNEdyX0xBSkZOdGduN080THhRLWNrRzNRV2piY1hPSkNOaDZxcWh0a2NnNzZOR2hGeHR4Rkh2QjdVNDlDdXhlcFhlRVB5R0JEUHp4c1lhRFh6bmdJdWlRU1h1WEhkQ2VONEhrUWZBVnRJRl81SE1sN0Z3dGx6dGxTd2NDUzYxM01oVHdKTVRVMDlXZXMxZmF0SnFrTjNPUjZtZlRtamVwTmZxaG1SLWtMYWxaa1E3OEVFTlBkQkRQb2ZIQ1AtSkdPVXRwQUN4aHBtdmZXVnNQYUtydUxzeXTSAf8BQVVfeXFMUEtWemJJN0VvVFA5R2c0WE43dWdwQW1qaXZBMGZzdUlzVWc3NXI1LWE1cE9ZT05Fb2JRbVAxdUdVSHZhWVpwa2VDU0NVbFBSNHVZZnNFZVdQN0loOVlUeUtKMll4d2xLclh3dXhTYVZSM3dHNXBSWXNMUGhydEcwYU1Lc1B5RHU4cEpQclFNNEZMZXZjeUp6QjVCc3l2anp4Ymw0M0VmNU9kQ2hlaUMtZ1c4VTg5eWF2eXhoMXh0UERTSUdORlcwQ0hCUDZTd21GUEdVYVM4aEFVTi1mWUxzbVZyUnhQdGhfcF9wdmxzSUtDYmh1dGVqX0pFa1g2QnFV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Livro A Rota do Calcário traz fatos curiosos sobre a história econômica de Arcos - Jornal Correio Centro Oeste Arcos</t>
+          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>13/07/2026 16:03</t>
+          <t>14/07/2026 04:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPazk4R0l0bkdTOGVENHBvc195X3hZMmFrTVBlNXlSMl9SWENKRllNV2Q3THJ5R3k0RW9Qc3lXOXdzeld4WkFZVlN1cWpPZXhNQlRPUXo0ODhnRXlkdEUySEtUNXRucGE5cjJKR1QzTklOdjdocUdvVmszcElRcVh2QlZYVzVLSTkwZThVMWJ1WTBKR3BtMTBSSGhEa0xFUzI4OXdRREdMamhsN19GdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Casa Criativa promove semana de férias com oficinas, teatro, filmes e muita diversão gratuita em Catalão e Ouvidor - Zap Catalão</t>
+          <t>Tensão em Ormuz afeta produção de fertilizantes no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>13/07/2026 14:18</t>
+          <t>14/07/2026 04:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOejBEaUdtTEdxREZwZTI2YndVVkttcDFZUkJtbU52akVtalBuaVluaGFFR2RxcElXbGNEYmU1ZV9Sb1h0UkpuT0ZsNWlCcGE4aXp0Z25xeVg2WUgzSHBFeVhJVXRYc1RsQkNpX0c5cHd1cGthREdrMHF6bFctZ1ByYlhybld0VGZBdWFzVHdNbjV1Z0FmQy1UMGNmZXZvWFdub0dHdGFGdDJfN3ktZ21XaGo2c25nMEV6dUdVNmtacm9idGJQczl5MjdxTXphbm4wV1FZV0xtTENodHVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaU1rV2NIc09fUTUwZVc4TEI3NEhSZ19UcHVqdEJKaDJ5dDNqSDdUaGo2VXlpWUp6OEpoRnU4ZEpCb2MxQ1RURXV3S3dreU1Lc24tVk8wazB0OTBsN2RIMmVER0ROd2hxUE1QOEdPMFZkc01MQVlHcWdDNDN1dVNETzFQQV94cDFwV0VzeGozdldYbXBBMkQ0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
+          <t>Livro A Rota do Calcário traz fatos curiosos sobre a história econômica de Arcos - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>13/07/2026 04:00</t>
+          <t>13/07/2026 16:03</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPazk4R0l0bkdTOGVENHBvc195X3hZMmFrTVBlNXlSMl9SWENKRllNV2Q3THJ5R3k0RW9Qc3lXOXdzeld4WkFZVlN1cWpPZXhNQlRPUXo0ODhnRXlkdEUySEtUNXRucGE5cjJKR1QzTklOdjdocUdvVmszcElRcVh2QlZYVzVLSTkwZThVMWJ1WTBKR3BtMTBSSGhEa0xFUzI4OXdRREdMamhsN19GdWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes inicia hibernação em Uberaba devido a falta de enxofre - Canal Rural</t>
+          <t>Casa Criativa promove semana de férias com oficinas, teatro, filmes e muita diversão gratuita em Catalão e Ouvidor - Zap Catalão</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>13/07/2026 04:00</t>
+          <t>13/07/2026 14:18</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOV3NNYmk3Z2wtOE5EbW1waDVvbU1Wem1BWU1RcVc1SDNFN1FsZkZXcFFmMkxVYzh0Uml6dlJBcVBmdk9wbDI0cTVEU0lEbWNRc0hnYkZvRFdaYS1rXzFVWDBYRkZmLTA0bldYdERnQ3BRazJFNzdOYUVFZ3M3RFlHbE00YkNydXFaN1ljSEVlelNxMlFzQ0c5N3dqVGxBb095a1pLSGkwa1NZX2trQUJuZFJjMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOejBEaUdtTEdxREZwZTI2YndVVkttcDFZUkJtbU52akVtalBuaVluaGFFR2RxcElXbGNEYmU1ZV9Sb1h0UkpuT0ZsNWlCcGE4aXp0Z25xeVg2WUgzSHBFeVhJVXRYc1RsQkNpX0c5cHd1cGthREdrMHF6bFctZ1ByYlhybld0VGZBdWFzVHdNbjV1Z0FmQy1UMGNmZXZvWFdub0dHdGFGdDJfN3ktZ21XaGo2c25nMEV6dUdVNmtacm9idGJQczl5MjdxTXphbm4wV1FZV0xtTENodHVo?oc=5</t>
         </is>
       </c>
     </row>
@@ -3785,44 +3785,44 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Demissão Mosaic Bahia: 500 funcionários serão demitidos - Associação Comercial e Industrial de Araçatuba</t>
+          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>11/07/2026 01:40</t>
+          <t>13/07/2026 04:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB2bXdPVjU4Rmg1U1NwYk9rUnpnbHBSZEgxc3VxcGdabmRCMVVBRXpfMnB5eHRUUFJXT3R5Q3lEWS1YQlNGTnNmZ05OSlEweDljT2lyUkVXYnRiQ2hPdTJnZHQ5cHJUbFoxdEFEbjFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>"Calcário convencional: herança do passado, desafios do futuro" - Revista Attalea Agronegócios</t>
+          <t>Mosaic Fertilizantes inicia hibernação em Uberaba devido a falta de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>10/07/2026 08:32</t>
+          <t>13/07/2026 04:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRXBKODRUMjRqNVVvbmlITmlfVVNET045UHpPY0FoeldGMU5QZXRDdE9YTDU1WExQcXBOUHRTUlVoek1xUjc2NGxwVVhCcjNTV2t4RDlZZFBkY3l3OGZfZDZYNnFCczJ1b25MTmpmMGQ1MkwwVnBISmNOX25jd3BNRnI0NEJMU2ZZVlEtZTVCejlOSFlDdXBDc3dxaEtycEFaSUdwSE00MHhHQWZZQWZGdk5kTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOV3NNYmk3Z2wtOE5EbW1waDVvbU1Wem1BWU1RcVc1SDNFN1FsZkZXcFFmMkxVYzh0Uml6dlJBcVBmdk9wbDI0cTVEU0lEbWNRc0hnYkZvRFdaYS1rXzFVWDBYRkZmLTA0bldYdERnQ3BRazJFNzdOYUVFZ3M3RFlHbE00YkNydXFaN1ljSEVlelNxMlFzQ0c5N3dqVGxBb095a1pLSGkwa1NZX2trQUJuZFJjMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -3834,39 +3834,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fosfato no Brasil por restrições no fornecimento de enxofre - Canal Rural</t>
+          <t>Demissão Mosaic Bahia: 500 funcionários serão demitidos - Associação Comercial e Industrial de Araçatuba</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>10/07/2026 04:00</t>
+          <t>11/07/2026 01:40</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPeG9YelAzMGdHdy0zZUNKcE9xYUczeVNvb3cxZTVPMEkyLXhUeTNHOUhDRU5hRjdZMzdZT2JzYlNGRW1oUzBPbHRKSnV2WXVlZFRYZ0F2Y3I0RHZxUWpMM3JKMEk5SG4yLTcyTk1PcjhpZFEwYmhKekVEY25razQyeEJURU5SMmE1NGIybVozNTJ2dldsemk4elE4LXhNa3BOeUdDZzBiWi03R0FaWWhYa3ctb1pEcEZhaWgwcldUVTl0MUtoV2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB2bXdPVjU4Rmg1U1NwYk9rUnpnbHBSZEgxc3VxcGdabmRCMVVBRXpfMnB5eHRUUFJXT3R5Q3lEWS1YQlNGTnNmZ05OSlEweDljT2lyUkVXYnRiQ2hPdTJnZHQ5cHJUbFoxdEFEbjFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
+          <t>"Calcário convencional: herança do passado, desafios do futuro" - Revista Attalea Agronegócios</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>10/07/2026 04:00</t>
+          <t>10/07/2026 08:32</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRXBKODRUMjRqNVVvbmlITmlfVVNET045UHpPY0FoeldGMU5QZXRDdE9YTDU1WExQcXBOUHRTUlVoek1xUjc2NGxwVVhCcjNTV2t4RDlZZFBkY3l3OGZfZDZYNnFCczJ1b25MTmpmMGQ1MkwwVnBISmNOX25jd3BNRnI0NEJMU2ZZVlEtZTVCejlOSFlDdXBDc3dxaEtycEFaSUdwSE00MHhHQWZZQWZGdk5kTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
+          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - G1</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOWTREUFFrb3B2UGF1dWRjQmhXM3lTdFJEX0JyRUhPSWp5R3ZicTk2YWh1YnBwbXpTbnpRSnZ6cUQ3aUx1LVU4b0dub1E2WkFfUnlHZzNmTG1VSkNVYVYzci0tbzRuX2hxSmpRRXlvYzlUcVAwSFdKbXVTOVlqSjlvcGllMVA0YWF0QlhnV2xKYmkyU1FxSlFoam5vcFVFQWZSekhqOFUtc0RNZXJ3eUlmS1VMY0J0cmxXbHlZczZWTjFfNmswMGh3VXRpMXJ6a0RYekhnZFZmUmlKTFl0RHBQUUdzRdIB8gFBVV95cUxNT1QwMkdFYWF6R1V3NHpfSVBHZFFDbHNhTzVOQkFSMmkweGxLaldvZXhOY0I5SkFObWJCcWlmN1FZdk9zOHVwMVZIck5oZHJEb2pRakltU01QS2prLWZublBLekVpNGtHY1JHNlhObHRlelRBM0ZGaTNwTkFZaUNFMTZBNkV1SEZSOWMzRndwd3h5ZGZhdWprczhBOXNlbF9NMlBsV0tEdVFQUXhnT1BMdjdCbnVKY3BWdzVUeDdWLV9HTDZGeVFMd3h1OS1jTWlIMnROQlc5VnRFUmE2VnpXVXJ3Vl9QSGZZTVNhdkFVZE9NZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - G1</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3910,19 +3910,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOWTREUFFrb3B2UGF1dWRjQmhXM3lTdFJEX0JyRUhPSWp5R3ZicTk2YWh1YnBwbXpTbnpRSnZ6cUQ3aUx1LVU4b0dub1E2WkFfUnlHZzNmTG1VSkNVYVYzci0tbzRuX2hxSmpRRXlvYzlUcVAwSFdKbXVTOVlqSjlvcGllMVA0YWF0QlhnV2xKYmkyU1FxSlFoam5vcFVFQWZSekhqOFUtc0RNZXJ3eUlmS1VMY0J0cmxXbHlZczZWTjFfNmswMGh3VXRpMXJ6a0RYekhnZFZmUmlKTFl0RHBQUUdzRdIB8gFBVV95cUxNT1QwMkdFYWF6R1V3NHpfSVBHZFFDbHNhTzVOQkFSMmkweGxLaldvZXhOY0I5SkFObWJCcWlmN1FZdk9zOHVwMVZIck5oZHJEb2pRakltU01QS2prLWZublBLekVpNGtHY1JHNlhObHRlelRBM0ZGaTNwTkFZaUNFMTZBNkV1SEZSOWMzRndwd3h5ZGZhdWprczhBOXNlbF9NMlBsV0tEdVFQUXhnT1BMdjdCbnVKY3BWdzVUeDdWLV9HTDZGeVFMd3h1OS1jTWlIMnROQlc5VnRFUmE2VnpXVXJ3Vl9QSGZZTVNhdkFVZE9NZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWjlvdWJTZGZFS0lpRFVleTl2bDV3WWlrazRpXzhuaXp2ZzRtWEUwcVh5dE02VldqaDlza0t2QnB4SXBuV29WVnY2Ti10MF9WN3NhaXViUk4zeXI5YkpUZWpHYWtuOUxsQV8xM2hrN05Edm5OaVMtMXlxT0NON2VYM3F4ek9BTjZ6bWQwS3l6aHF0NzlfMmttd0FqY0pFR0VRRWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre - brasilagro.com.br</t>
+          <t>Após tombo nos preços, ureia entra em fase de recuperação - agrolink.com.br</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWjlvdWJTZGZFS0lpRFVleTl2bDV3WWlrazRpXzhuaXp2ZzRtWEUwcVh5dE02VldqaDlza0t2QnB4SXBuV29WVnY2Ti10MF9WN3NhaXViUk4zeXI5YkpUZWpHYWtuOUxsQV8xM2hrN05Edm5OaVMtMXlxT0NON2VYM3F4ek9BTjZ6bWQwS3l6aHF0NzlfMmttd0FqY0pFR0VRRWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOWTRuMG5FVXRzbW5lbTZ4Q182YW9hSUFwWUphaDFuZHlISXZHNEhtX1drcjdFTDZlYWpCNFNqR2l6cDlsMjRrbGxVRnViZWNIZWJ1Q0h4RzRmbzZoVVczNEpyQ0MzZ0FqeUQ3VWw3QjFCdU1qdlJrdmV5WlpSTlJHZ3ZUOFptXzhqR3hqbEV1UTZ4TzYzZExLX0hnSWZLekdacmJMbEtiME1rUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Após tombo nos preços, ureia entra em fase de recuperação - Agrolink</t>
+          <t>Mosaic reduz produção de fosfato no Brasil por restrições no fornecimento de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3954,29 +3954,29 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOWTRuMG5FVXRzbW5lbTZ4Q182YW9hSUFwWUphaDFuZHlISXZHNEhtX1drcjdFTDZlYWpCNFNqR2l6cDlsMjRrbGxVRnViZWNIZWJ1Q0h4RzRmbzZoVVczNEpyQ0MzZ0FqeUQ3VWw3QjFCdU1qdlJrdmV5WlpSTlJHZ3ZUOFptXzhqR3hqbEV1UTZ4TzYzZExLX0hnSWZLekdacmJMbEtiME1rUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPeG9YelAzMGdHdy0zZUNKcE9xYUczeVNvb3cxZTVPMEkyLXhUeTNHOUhDRU5hRjdZMzdZT2JzYlNGRW1oUzBPbHRKSnV2WXVlZFRYZ0F2Y3I0RHZxUWpMM3JKMEk5SG4yLTcyTk1PcjhpZFEwYmhKekVEY25razQyeEJURU5SMmE1NGIybVozNTJ2dldsemk4elE4LXhNa3BOeUdDZzBiWi03R0FaWWhYa3ctb1pEcEZhaWgwcldUVTl0MUtoV2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Luiz Armando Costa</t>
+          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>09/07/2026 06:50</t>
+          <t>10/07/2026 04:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMWpueTF3aVVYMWVnUU5aWHduSWUyZy1jNzBCWXlLZl9qQ3pTMnY0MmFhY2twNXk4V0ZaNy1oU0c3SHlrZi1KTV9pVUhvdW5EVnl1MnJEaHB0UF9rVTcwTnhCLWcwM0N6cTFSUEhfUHBscDF6WTRZcDFFUFk5R2ZxaDJmQ3FGUHgyQUF2RDJnWURZRm5EdWYzTDI4aGphekttRjY1Zm5POTFqc2lhWTdoTWxDYUo4QnpLbkpZN3lGLVY4dFVIRVVIYXRwaEp4YUhuT1BWOWw4WDJTTVc0X1Jvc1NfVjlST0NR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3988,51 +3988,51 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
+          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - moneytimes.com.br</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>09/07/2026 04:00</t>
+          <t>10/07/2026 04:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
+          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Luiz Armando Costa</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>09/07/2026 04:00</t>
+          <t>09/07/2026 06:50</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMWpueTF3aVVYMWVnUU5aWHduSWUyZy1jNzBCWXlLZl9qQ3pTMnY0MmFhY2twNXk4V0ZaNy1oU0c3SHlrZi1KTV9pVUhvdW5EVnl1MnJEaHB0UF9rVTcwTnhCLWcwM0N6cTFSUEhfUHBscDF6WTRZcDFFUFk5R2ZxaDJmQ3FGUHgyQUF2RDJnWURZRm5EdWYzTDI4aGphekttRjY1Zm5POTFqc2lhWTdoTWxDYUo4QnpLbkpZN3lGLVY4dFVIRVVIYXRwaEp4YUhuT1BWOWw4WDJTTVc0X1Jvc1NfVjlST0NR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
+          <t>Dano ambiental em Catalão leva mineradora a fazer acordo milionário - Mais Goiás</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4042,19 +4042,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPSldVaDI4S0tmbkFoaXp5UUZ2WUJuNlZOM1Q2RGJEbkJ6RW9ERXk5VjAwV3p2QjkyODF6Ni0wZk0wbEJxdlZueFhKMWJHQlU0RHRlUnU2RVdmM2ZKaHAzZU5LdUNoWlNxc0pTX2JCOU1vRWljaGpyemx2SG1pUU1UbWpkeXdEd2JLTWd2SGRoRnBRZjdKR3JpcDZTb25YUllJWnFEVUZkN0hoSFladUJ1ZFdGend1YVpmd0FxNVlONkdXeU9ZaVdIdTRTWkZTNGw1dkdV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dano ambiental em Catalão leva mineradora a fazer acordo milionário - Mais Goiás</t>
+          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPSldVaDI4S0tmbkFoaXp5UUZ2WUJuNlZOM1Q2RGJEbkJ6RW9ERXk5VjAwV3p2QjkyODF6Ni0wZk0wbEJxdlZueFhKMWJHQlU0RHRlUnU2RVdmM2ZKaHAzZU5LdUNoWlNxc0pTX2JCOU1vRWljaGpyemx2SG1pUU1UbWpkeXdEd2JLTWd2SGRoRnBRZjdKR3JpcDZTb25YUllJWnFEVUZkN0hoSFladUJ1ZFdGend1YVpmd0FxNVlONkdXeU9ZaVdIdTRTWkZTNGw1dkdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
         </is>
       </c>
     </row>
@@ -4076,17 +4076,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
+          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>08/07/2026 11:07</t>
+          <t>09/07/2026 04:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a775a9e34a141918d41567397f35617&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4098,51 +4098,51 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>08/07/2026 04:00</t>
+          <t>09/07/2026 04:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>08/07/2026 04:00</t>
+          <t>08/07/2026 11:07</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a7772a23aa2412eaab3ff2d4ce68db7&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil - CNN Brasil</t>
+          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4152,19 +4152,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcUJxWVBXU2s0ODBmWkpuckdwbG1wa0p1T1ZnRDkta25heDI5VVZZWC1hb3JfeEhzUTJHWUlJUnBScVJYSGFQWXdYRE1rU0JTYjJzQ21JODBlMlpfU3NJdy10UVo0NDRrejRvNGRBSUlZZUl5Zl8wMlV1VXROUi05VjZoZVVSckpWN2hRUHVvaE55WHM1RWJGdkE2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Justiça homologa acordo de R$ 11 milhões para reparação ambiental em Catalão - Tribuna do Planalto</t>
+          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4174,19 +4174,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQN1d3cHVseUJvTWtEQTVYQUZNVGV0MGJ0MlNTS0VDaVFlNFlVNGxwNXpCcndCaHpDYm13OXFHOHppZF9kcHZhc1Zjd2F2VWhzOVIwalFRRjh5VE9kMmhPZXNCcnJKb1ctQmJta2VWV3NTVHZSaVJyTDN0YVlqWHhpV0JLT3dpbmpSVXpleW5RNlpFMGE3SWtxemplY0c1czJIcVAtbHlwWm5sREtSR1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - Prefeitura Municipal de Sorriso</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4196,19 +4196,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcUJxWVBXU2s0ODBmWkpuckdwbG1wa0p1T1ZnRDkta25heDI5VVZZWC1hb3JfeEhzUTJHWUlJUnBScVJYSGFQWXdYRE1rU0JTYjJzQ21JODBlMlpfU3NJdy10UVo0NDRrejRvNGRBSUlZZUl5Zl8wMlV1VXROUi05VjZoZVVSckpWN2hRUHVvaE55WHM1RWJGdkE2QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre - Globo Rural</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4218,19 +4218,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeURESU1tOVZJdTFPMTAtOVJ0RzVaV2dwZGI4VklqWm5qTUVLRnR5NkZUVC1GQ3lJaEg0YjJNS0JLSDVhT1JGXzZ5UDUzWGY0YXB4bmZDYmdpMlI2WkpLUG1zeVJ6VUN6VHRGbGNaMWd2aU9kQkJlbFhTd2kxZGlRMFZMWDZhWjNkeVNoam9Ya053dzhjeGFETWJySEhadVpkUFN3TjAya2dXNTVIeFJvZ0ZVc1dIZ9IBxAFBVV95cUxQcnRNVFl3amU0YlA0UU82NnRxOVo3c2Q0MkxIdGtLN0JvZ0pGLUtMTmxSME5VTjBZWkJ0UmZvU3ZCWVJwM29iWnN5RWtwb3ZFWGFraVRpLWlWWnJCWndRemlKdnBaQ2J6eG96RjZ0dEdWbzBFUXlzT1gweTQwWGtrRGhRSjVwejFXY0NxY1dsSUZ0S2k4aHc1TG1fN2hLZFdNb3R5MjlGeUxibEctMU9yenF2UFplUHlDdlNOdko0cWhCb1BP?oc=5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre - Globo Rural</t>
+          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - Prefeitura Municipal de Sorriso</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4240,73 +4240,73 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeURESU1tOVZJdTFPMTAtOVJ0RzVaV2dwZGI4VklqWm5qTUVLRnR5NkZUVC1GQ3lJaEg0YjJNS0JLSDVhT1JGXzZ5UDUzWGY0YXB4bmZDYmdpMlI2WkpLUG1zeVJ6VUN6VHRGbGNaMWd2aU9kQkJlbFhTd2kxZGlRMFZMWDZhWjNkeVNoam9Ya053dzhjeGFETWJySEhadVpkUFN3TjAya2dXNTVIeFJvZ0ZVc1dIZ9IBxAFBVV95cUxQcnRNVFl3amU0YlA0UU82NnRxOVo3c2Q0MkxIdGtLN0JvZ0pGLUtMTmxSME5VTjBZWkJ0UmZvU3ZCWVJwM29iWnN5RWtwb3ZFWGFraVRpLWlWWnJCWndRemlKdnBaQ2J6eG96RjZ0dEdWbzBFUXlzT1gweTQwWGtrRGhRSjVwejFXY0NxY1dsSUZ0S2k4aHc1TG1fN2hLZFdNb3R5MjlGeUxibEctMU9yenF2UFplUHlDdlNOdko0cWhCb1BP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PACAEMBU: AGROPAC AGROPECUÁRIA é referência no fornecimento de calcário e gesso agrícola - folharegionalnet.com.br</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>07/07/2026 04:00</t>
+          <t>08/07/2026 04:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxORkNZS1FFSTJ3WjdYWW1tTjduTnR4cUFSODg0cm5YM1BKZnlzbDFueTgyVmlYX0tiYzlHRG1pMHhoYnRKNVg5YzU1dGJobks0RGIzTEU2NldoYWNFLV8xV1hOYl90WVRwMTYzUWpCbWtoRkE2WU1TYjJyenlfZzZrVjlvOXJselhmS2xjOWtZa1h6LUtxUGtLQ0w0MGVMdEVSTzhReDdJelIzUW1reENDRXAwaGJVWFlwNFJqOGx3N1NmRExzYng0a0lR0gHPAUFVX3lxTFBrYW15bDIyRUFjVWxyamdjOG5fMEpxeHZuSVVTenhrdkY4VXZZSU5HNHR6aU5GekY0ZFlxMmEwTWVpZFg3VlIwMHlSamZOR3pxNW12WWU3ZWVPeEQ4ZW1TRzE4VHpkUWlfN2M5Q202M1BSUVRhdFpIaXJVRElqVE1GYzFyOVNKN25uWlhPSUdlT3h3SGtLMjgycUdvNlFQdEF5RjNhaXNWeW5FclZKXzh3ZkhYUjMxOEdlWTlHYTdzWkh0WjlRdG85WDlPYVFvbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
+          <t>Justiça homologa acordo de R$ 11 milhões para reparação ambiental em Catalão - Tribuna do Planalto</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>06/07/2026 04:00</t>
+          <t>08/07/2026 04:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQN1d3cHVseUJvTWtEQTVYQUZNVGV0MGJ0MlNTS0VDaVFlNFlVNGxwNXpCcndCaHpDYm13OXFHOHppZF9kcHZhc1Zjd2F2VWhzOVIwalFRRjh5VE9kMmhPZXNCcnJKb1ctQmJta2VWV3NTVHZSaVJyTDN0YVlqWHhpV0JLT3dpbmpSVXpleW5RNlpFMGE3SWtxemplY0c1czJIcVAtbHlwWm5sREtSR1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Fertilizantes subiram mais que a inflação desde 2016; ureia ainda custa 149% a mais em termos reais - Agrolink</t>
+          <t>PACAEMBU: AGROPAC AGROPECUÁRIA é referência no fornecimento de calcário e gesso agrícola - folharegionalnet.com.br</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>04/07/2026 04:00</t>
+          <t>07/07/2026 04:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOTEZVZTZETDBfN3VETnZRZ1lwamFoV1dlYzJCS3NSQlZaaHdMbXZyM0xUT2JKRWZId3Z3ZDc4VlJjc0s0VDJ5M1hTMnJYclpYZDlEZmxrQVhPXzR3UDBUSkxLc0xGU1lPcWQ2UDROZllLMzdlNHhGTG5RNGtDVGJTbVRPR3BWcGw1YlpvdXVTYnVrSXMzaGE1d1Z1a0dGcWJUSWZqTFUxRERITWVSQUU1eWhTTFBCaFlLa0NFWHFvUDROVnJQbjRyVU1wS25KNmdyX0psZ3lGeW92TTBYYlYzUlVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxORkNZS1FFSTJ3WjdYWW1tTjduTnR4cUFSODg0cm5YM1BKZnlzbDFueTgyVmlYX0tiYzlHRG1pMHhoYnRKNVg5YzU1dGJobks0RGIzTEU2NldoYWNFLV8xV1hOYl90WVRwMTYzUWpCbWtoRkE2WU1TYjJyenlfZzZrVjlvOXJselhmS2xjOWtZa1h6LUtxUGtLQ0w0MGVMdEVSTzhReDdJelIzUW1reENDRXAwaGJVWFlwNFJqOGx3N1NmRExzYng0a0lR0gHPAUFVX3lxTFBrYW15bDIyRUFjVWxyamdjOG5fMEpxeHZuSVVTenhrdkY4VXZZSU5HNHR6aU5GekY0ZFlxMmEwTWVpZFg3VlIwMHlSamZOR3pxNW12WWU3ZWVPeEQ4ZW1TRzE4VHpkUWlfN2M5Q202M1BSUVRhdFpIaXJVRElqVE1GYzFyOVNKN25uWlhPSUdlT3h3SGtLMjgycUdvNlFQdEF5RjNhaXNWeW5FclZKXzh3ZkhYUjMxOEdlWTlHYTdzWkh0WjlRdG85WDlPYVFvbw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4318,127 +4318,127 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
+          <t>Enxofre ganha espaço no manejo das lavouras - agrolink.com.br</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>03/07/2026 04:00</t>
+          <t>06/07/2026 04:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
+          <t>Fertilizantes subiram mais que a inflação desde 2016; ureia ainda custa 149% a mais em termos reais - agrolink.com.br</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>03/07/2026 04:00</t>
+          <t>04/07/2026 04:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOTEZVZTZETDBfN3VETnZRZ1lwamFoV1dlYzJCS3NSQlZaaHdMbXZyM0xUT2JKRWZId3Z3ZDc4VlJjc0s0VDJ5M1hTMnJYclpYZDlEZmxrQVhPXzR3UDBUSkxLc0xGU1lPcWQ2UDROZllLMzdlNHhGTG5RNGtDVGJTbVRPR3BWcGw1YlpvdXVTYnVrSXMzaGE1d1Z1a0dGcWJUSWZqTFUxRERITWVSQUU1eWhTTFBCaFlLa0NFWHFvUDROVnJQbjRyVU1wS25KNmdyX0psZ3lGeW92TTBYYlYzUlVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
+          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>01/07/2026 04:00</t>
+          <t>03/07/2026 04:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>30/06/2026 04:00</t>
+          <t>03/07/2026 04:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Programa Terra Boa 2026 garante distribuição gratuita de calcário para fortalecer a agricultura em Navegantes - Prefeitura de Navegantes -</t>
+          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>29/06/2026 04:00</t>
+          <t>01/07/2026 04:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQYlpYdmcxN2o2cDRhamVVcW5PQjNBTDdLd05XZDIzUDJrd0ZuOTVwUHg1SUlqb2pXamZGMXZmODZjRTlSOU11YnpINUk1bnhkUjhrWjFZX1RlQWUxVDV2UEIzbU83N09lWTBadmlEdnJVcm1uZ2d3a1pGeFFLcGlGYndtLUJHWVJjSS1Bc0UwRHdpNlJMbzJJTjREVm5ocDhHay16VTdrbVZ1NWhzb0dPOHFkWTAza25ENVZSSDFDdk94dnFYZGZMcVFNNDktekVwMjhvQVN2Zk9UVHppem5vcFl2SEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ureia, MAP e potássio registram queda no Brasil - Agrolink</t>
+          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>29/06/2026 04:00</t>
+          <t>30/06/2026 04:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQckZkR0twcU1KM1hzRlBoYnlKaEVXbERoOEJfSk5zLVJHSlFXc2pVS0hqRlQ0djV0b2o5NDY0azg3REJLbnBlaVJ2VWZ6Y2lzaVF4STlrWlh4TDcteXBGN29xWDdTc0hmU1pROF9UZ2d4UlR0bGFtNjd6UzZqakxCeGlHTEZRTUVReHllcG5NOFV4OFRXZ05YZTIySlg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
+          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4504,51 +4504,51 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
+          <t>Ureia, MAP e potássio registram queda no Brasil - agrolink.com.br</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>28/06/2026 04:00</t>
+          <t>29/06/2026 04:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQckZkR0twcU1KM1hzRlBoYnlKaEVXbERoOEJfSk5zLVJHSlFXc2pVS0hqRlQ0djV0b2o5NDY0azg3REJLbnBlaVJ2VWZ6Y2lzaVF4STlrWlh4TDcteXBGN29xWDdTc0hmU1pROF9UZ2d4UlR0bGFtNjd6UzZqakxCeGlHTEZRTUVReHllcG5NOFV4OFRXZ05YZTIySlg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Embarques de fertilizantes crescem após acordo no estreito de Ormuz - CNN Brasil</t>
+          <t>Programa Terra Boa 2026 garante distribuição gratuita de calcário para fortalecer a agricultura em Navegantes - Prefeitura de Navegantes -</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>29/06/2026 04:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcENnZnlBVWF1ZEVFeElfLU56Y1RaZ2ZiQkdOck1KdnJkbzUwa1Z3dUo3aTItQmJrRjNKVVZKLW9NNHdhSE9FejZXb3ZiMDZZSTBGdk16SmZ2ckd1UHB2TXlNYnFZc1c2V0hlaXF4ZEpRT1pWcktSM055QXBtS3d2bVMtU1BFWkRkQmt6alZiYWFldVR0ZWp1N2hGMjRFLUlnMkxNTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQYlpYdmcxN2o2cDRhamVVcW5PQjNBTDdLd05XZDIzUDJrd0ZuOTVwUHg1SUlqb2pXamZGMXZmODZjRTlSOU11YnpINUk1bnhkUjhrWjFZX1RlQWUxVDV2UEIzbU83N09lWTBadmlEdnJVcm1uZ2d3a1pGeFFLcGlGYndtLUJHWVJjSS1Bc0UwRHdpNlJMbzJJTjREVm5ocDhHay16VTdrbVZ1NWhzb0dPOHFkWTAza25ENVZSSDFDdk94dnFYZGZMcVFNNDktekVwMjhvQVN2Zk9UVHppem5vcFl2SEM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4560,29 +4560,29 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
+          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>28/06/2026 04:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Visão Agro</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4592,19 +4592,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNeV9TQXlwdXdzSXF6T3hnTmlVZ3dJLUFRQnAwTDZSMG50ZjUzTkR6V3RfT1dXOE82VW9WSU1vTEhjbkNmOElfVTZDWVNMMnNvNkJmTld0M2Y0ZEIzT0NfQ09SeC10RTZMMlpFRHFCMEpMSDk5Vy1EYjdtaURFT1dmWXNaME9DcGZGbVlDN3BTUm9qVnBh?oc=5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Crise dos fertilizantes: estoque baixo de enxofre ameaça a próxima safra - band.com.br</t>
+          <t>Ureia despenca após trégua no Oriente Médio - agrolink.com.br</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQdGoxOXo2NXl5WnpUd3E1ZWQ5RldtTUR2M0F6YnljMXNxb2NVM0RrVDY3WTE5SExJYzdmbzZPYlFlOXhrUTRoZnJ2amFPR2wzNGlVd2JTNDhzYkplbHVET0pJeTh0U292YmtkT1NPb01lY1JyRDk5MG9TaTNEZHQ3ZjlJU0lXNXJJTkRWZUNFbUtUbmdPN3oxX3Z4cVJvWWdtRks4TV9VcXM3SjduOElxckFTSGpncTNJb01YUllNa0RNTmYtVm53T2lHYlJPTEV5ajVCQk1wQThIMnU5aWtHSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
         </is>
       </c>
     </row>
@@ -4626,149 +4626,149 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
+          <t>Embarques de fertilizantes crescem após acordo no estreito de Ormuz - CNN Brasil</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcENnZnlBVWF1ZEVFeElfLU56Y1RaZ2ZiQkdOck1KdnJkbzUwa1Z3dUo3aTItQmJrRjNKVVZKLW9NNHdhSE9FejZXb3ZiMDZZSTBGdk16SmZ2ckd1UHB2TXlNYnFZc1c2V0hlaXF4ZEpRT1pWcktSM055QXBtS3d2bVMtU1BFWkRkQmt6alZiYWFldVR0ZWp1N2hGMjRFLUlnMkxNTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
+          <t>Crise dos fertilizantes: estoque baixo de enxofre ameaça a próxima safra - band.com.br</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>23/06/2026 04:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQdGoxOXo2NXl5WnpUd3E1ZWQ5RldtTUR2M0F6YnljMXNxb2NVM0RrVDY3WTE5SExJYzdmbzZPYlFlOXhrUTRoZnJ2amFPR2wzNGlVd2JTNDhzYkplbHVET0pJeTh0U292YmtkT1NPb01lY1JyRDk5MG9TaTNEZHQ3ZjlJU0lXNXJJTkRWZUNFbUtUbmdPN3oxX3Z4cVJvWWdtRks4TV9VcXM3SjduOElxckFTSGpncTNJb01YUllNa0RNTmYtVm53T2lHYlJPTEV5ajVCQk1wQThIMnU5aWtHSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
+          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>23/06/2026 04:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>22/06/2026 04:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
+          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>22/06/2026 04:00</t>
+          <t>23/06/2026 04:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
+          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>22/06/2026 04:00</t>
+          <t>23/06/2026 04:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
         </is>
       </c>
     </row>
@@ -4780,193 +4780,193 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
+          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>21/06/2026 04:00</t>
+          <t>22/06/2026 04:00</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
+          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>21/06/2026 04:00</t>
+          <t>22/06/2026 04:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
+          <t>Ureia despenca e volta aos níveis pré-guerra - agrolink.com.br</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>20/06/2026 04:00</t>
+          <t>22/06/2026 04:00</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
+          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>20/06/2026 04:00</t>
+          <t>21/06/2026 04:00</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
+          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>19/06/2026 04:00</t>
+          <t>21/06/2026 04:00</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Prefeituras têm até 30 de junho para retirar agrosilício - AMM | Associação Mineira de Municípios</t>
+          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>18/06/2026 04:00</t>
+          <t>20/06/2026 04:00</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNa2hNNldIOFhaOUVZS1JtcTJwUWRXT1dkU2F6NWwxR29SUmJCa2d2dUxNdnROS2RfQTFsSml2TUlaX3VZTXZzYWJCWTkyZlJuWVhnM2JqS3RiVGRwb21xbVR6dmlHQWdJM1dFdkgyUXBrR2NOVFZwUVgtcUdFMWhNa2ZleDZyV1FsOERLZElmb0I5amdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
+          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>17/06/2026 04:00</t>
+          <t>20/06/2026 04:00</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Atualização Chaos Cubed - Minecraft</t>
+          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>16/06/2026 14:20</t>
+          <t>19/06/2026 04:00</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
+          <t>Prefeituras têm até 30 de junho para retirar agrosilício - AMM | Associação Mineira de Municípios</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>16/06/2026 04:00</t>
+          <t>18/06/2026 04:00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOc2dmVzJBa0tyZGQ3T3dCOFlFZjhkQXg0SmFjUmltT3RmbVlKSDlfYm1vOHNDMG5kdTdDalcyQ3dmTTlyY00taHRwTVhRSE54ZUdjdEZNWVEwYkRmRV9JS0FOY0xIQ01ISUF3VHA5ZmVZVS1XdlA2Mzk1UUNEbHFuT1VyUFhYSWZlU2lVay0wYUl1WmFzaEg5VmpKaGw1OTFHdWlHdDBGWlpqUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNa2hNNldIOFhaOUVZS1JtcTJwUWRXT1dkU2F6NWwxR29SUmJCa2d2dUxNdnROS2RfQTFsSml2TUlaX3VZTXZzYWJCWTkyZlJuWVhnM2JqS3RiVGRwb21xbVR6dmlHQWdJM1dFdkgyUXBrR2NOVFZwUVgtcUdFMWhNa2ZleDZyV1FsOERLZElmb0I5amdF?oc=5</t>
         </is>
       </c>
     </row>
@@ -4978,83 +4978,83 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
+          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>16/06/2026 04:00</t>
+          <t>17/06/2026 04:00</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
+          <t>Atualização Chaos Cubed - Minecraft</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>15/06/2026 04:00</t>
+          <t>16/06/2026 14:20</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Calcário ganha espaço no campo após alta dos fertilizantes e pode beneficiar produtores do Nordeste - Paraíba Business</t>
+          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>15/06/2026 04:00</t>
+          <t>16/06/2026 04:00</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPdHRzWEdaMFMwRjhjQ2w2Z2I0VkNic0xRT2w5dTVkUVpUOWRVRkxFRG1sa3Yxbk80cGlrcWhiVExVVG15M3Npb2FyUU1tekhiSjZiOHV6ZGRqR2NOVzN3MTN1cUQ2SEZqTWI2Y3VGTEM3dVI2dnBHOU5pZ1Q5MVVKX2dueHF1RkoyTVRnamExN1ktcmoybUhtT2Q0WmZqYUZYb2NGaXNMUUtjWXFMdzFqYzhKTWFmZWpvb2YwUlN2TVRValViS1E1RnJtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
+          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>15/06/2026 04:00</t>
+          <t>16/06/2026 04:00</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOc2dmVzJBa0tyZGQ3T3dCOFlFZjhkQXg0SmFjUmltT3RmbVlKSDlfYm1vOHNDMG5kdTdDalcyQ3dmTTlyY00taHRwTVhRSE54ZUdjdEZNWVEwYkRmRV9JS0FOY0xIQ01ISUF3VHA5ZmVZVS1XdlA2Mzk1UUNEbHFuT1VyUFhYSWZlU2lVay0wYUl1WmFzaEg5VmpKaGw1OTFHdWlHdDBGWlpqUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5083,132 +5083,132 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
+          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>12/06/2026 04:00</t>
+          <t>15/06/2026 04:00</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - andravirtual.com.br</t>
+          <t>Calcário ganha espaço no campo após alta dos fertilizantes e pode beneficiar produtores do Nordeste - Paraíba Business</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>11/06/2026 04:00</t>
+          <t>15/06/2026 04:00</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPdHRzWEdaMFMwRjhjQ2w2Z2I0VkNic0xRT2w5dTVkUVpUOWRVRkxFRG1sa3Yxbk80cGlrcWhiVExVVG15M3Npb2FyUU1tekhiSjZiOHV6ZGRqR2NOVzN3MTN1cUQ2SEZqTWI2Y3VGTEM3dVI2dnBHOU5pZ1Q5MVVKX2dueHF1RkoyTVRnamExN1ktcmoybUhtT2Q0WmZqYUZYb2NGaXNMUUtjWXFMdzFqYzhKTWFmZWpvb2YwUlN2TVRValViS1E1RnJtZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
+          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>10/06/2026 04:00</t>
+          <t>15/06/2026 04:00</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
+          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>09/06/2026 04:00</t>
+          <t>12/06/2026 04:00</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
+          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - andravirtual.com.br</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>09/06/2026 04:00</t>
+          <t>11/06/2026 04:00</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
+          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>09/06/2026 04:00</t>
+          <t>10/06/2026 04:00</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5237,12 +5237,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
+          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5252,29 +5252,29 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
+          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>08/06/2026 14:39</t>
+          <t>09/06/2026 04:00</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
         </is>
       </c>
     </row>
@@ -5286,39 +5286,39 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
+          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>08/06/2026 14:33</t>
+          <t>09/06/2026 04:00</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
+          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>08/06/2026 10:32</t>
+          <t>09/06/2026 04:00</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5330,39 +5330,39 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
+          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>08/06/2026 04:00</t>
+          <t>08/06/2026 14:39</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Empresas ampliam vagas e buscam talentos - Terra</t>
+          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - cepea.org.br</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>08/06/2026 04:00</t>
+          <t>08/06/2026 14:33</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQVlV3clMtbWtWX1RVVWlfSUpxbm1YaW1oNk9MR3h1WDMyaWExaTNQZUVzTHR6TWdxOFJkVnVvTGI5cnVkRGpTeHJkV1hKNG5TZW52aGZlREEyUDZFTUJmcGM5TjJSTVhnN0c2dGFBZDlVcm9FelE5LW02VVVJSEZaU3JHeWxNaUNaVHFGYjNiZ0ozT2lTbVpORUF2UFhudWxENDI1QnJ6ekNKSmtBTFozckxkNXlCaHVoRjFSQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5374,83 +5374,83 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - agrolink.com.br</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>04/06/2026 04:00</t>
+          <t>08/06/2026 10:32</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
+          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>03/06/2026 04:00</t>
+          <t>08/06/2026 04:00</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em Tapira, devido à falta de enxofre e custo da matéria-prima - Jornal Araxá</t>
+          <t>Empresas ampliam vagas e buscam talentos - Terra</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>02/06/2026 12:15</t>
+          <t>08/06/2026 04:00</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeGt1SzZTRTQ4QkxZbXVuRmlZQWJIWlg5RGZkX0VuVTk2ZkVzMERUUy1CZ0dyU21qZTZQclpTd0ZUaXdMb21VZGszMHVldE1oYWI3UlhmZjUwV1V4em9zblNSd2lRT3c3eGhIdjlnOWxnanl0Sk5keW5DZjQ2cUYyR0RSUGZaU1NhNkFEYUw1TDVpOFdjRnZZLWVvNUlxRjZRZlppSHhFVFJoUGxNc1pkb0ZuNUc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQVlV3clMtbWtWX1RVVWlfSUpxbm1YaW1oNk9MR3h1WDMyaWExaTNQZUVzTHR6TWdxOFJkVnVvTGI5cnVkRGpTeHJkV1hKNG5TZW52aGZlREEyUDZFTUJmcGM5TjJSTVhnN0c2dGFBZDlVcm9FelE5LW02VVVJSEZaU3JHeWxNaUNaVHFGYjNiZ0ozT2lTbVpORUF2UFhudWxENDI1QnJ6ekNKSmtBTFozckxkNXlCaHVoRjFSQg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
+          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>02/06/2026 04:00</t>
+          <t>04/06/2026 04:00</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -5462,83 +5462,83 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
+          <t>Ureia recua e fosfatados seguem sustentados - agrolink.com.br</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>02/06/2026 04:00</t>
+          <t>03/06/2026 04:00</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
+          <t>Mosaic suspende operações em Tapira, devido à falta de enxofre e custo da matéria-prima - Jornal Araxá</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>01/06/2026 04:00</t>
+          <t>02/06/2026 12:15</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeGt1SzZTRTQ4QkxZbXVuRmlZQWJIWlg5RGZkX0VuVTk2ZkVzMERUUy1CZ0dyU21qZTZQclpTd0ZUaXdMb21VZGszMHVldE1oYWI3UlhmZjUwV1V4em9zblNSd2lRT3c3eGhIdjlnOWxnanl0Sk5keW5DZjQ2cUYyR0RSUGZaU1NhNkFEYUw1TDVpOFdjRnZZLWVvNUlxRjZRZlppSHhFVFJoUGxNc1pkb0ZuNUc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
+          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>01/06/2026 04:00</t>
+          <t>02/06/2026 04:00</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
+          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>01/06/2026 04:00</t>
+          <t>02/06/2026 04:00</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5567,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
+          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5582,19 +5582,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
+          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - clarim.net.br</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5604,73 +5604,73 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
+          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>31/05/2026 04:00</t>
+          <t>01/06/2026 04:00</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
+          <t>Ureia cai pela sexta semana seguida no Brasil - agrolink.com.br</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>31/05/2026 04:00</t>
+          <t>01/06/2026 04:00</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
+          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>31/05/2026 04:00</t>
+          <t>01/06/2026 04:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo resistente à umidade e ao vento - Paraná Central</t>
+          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5692,73 +5692,73 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOdk56ZUFYa2pGdWtqdzRMRjJNTmRzNExlY3pPSnpmZjVsQ2ZCT3pJeDl1UGk1dzR1bmRJYjB0akk5alp1YW83empGWHY2TVhzWXdfRHlrenRSRFNHUmx5dS1pLW83YXhWX3ZsSldMM3luSXNScEJRUUpNdTVBM3hTV2tFdDdnRkZvTkowU3IxbU1ZWTBiNVRKSXRhWi05QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
+          <t>Embrapa cria calcário mais nutritivo resistente à umidade e ao vento - Paraná Central</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>29/05/2026 04:00</t>
+          <t>31/05/2026 04:00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPWmY3TXBIbWxobnFjUi1mTUozS2xCbTlaSGxKX2o0QTExdWszWk5USkR4ZVk0Zk5vcTIxSm9HZDRzazlGVjBDLVE4a2NTTnQ4eHpQM3cyNTFDVDd1aGs0cFhxUVBmbXlaUTNLMjljT0FSRWlMRm1iVkxMYk1uc2Nvd0JZencteGFkLXNFSWxySlhTNkdpemo2Y2N4ZlFOclJPMkNLUDdGU2FrYTJsRjIzdTE3RWVQUnhGbXJpVkJhcWhjclZJaWdXM2dueTFYRjNfMWE5WjBEWEFxUdIB3wFBVV95cUxOdGxrd3ZlRXQ3X0k0Rkx5VDk0OW5yQ0FyZ1A1QW5wTGhXZDA3blVtaVdobkM5YVFBcEhsUUlYRGYwVlVodlF1UmxsbVZaY0c2Z2lScV9hWnlOdlpZYzZDNXVLWWdiU0FvRExxZlQzQ2d3N3lTbk9tY3pXZEpJOWtZaDhOYVhVOXFFWExTVkYyMU5jUnk3VURmS0dMazRJUERGYS1BS2p5MFo5bXg3eFlPcVJtZ1NMQjBYRDFrWmRRbnpRdWlMU0VmaHI3T2tHUGp2b3I3bFZZYk9oWWhDX3pN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOdk56ZUFYa2pGdWtqdzRMRjJNTmRzNExlY3pPSnpmZjVsQ2ZCT3pJeDl1UGk1dzR1bmRJYjB0akk5alp1YW83empGWHY2TVhzWXdfRHlrenRSRFNHUmx5dS1pLW83YXhWX3ZsSldMM3luSXNScEJRUUpNdTVBM3hTV2tFdDdnRkZvTkowU3IxbU1ZWTBiNVRKSXRhWi05QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Grand Prix SENAI 2026 conecta estudantes e grandes indústrias em maratona nacional de inovação - Agência de Notícias da Indústria</t>
+          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00</t>
+          <t>31/05/2026 04:00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNazFuZVlIdUdWeE55Y1hySHEyQnpEazJfaU1ING1DVlNVQ21nUWNVb2pBTE43ZlVwc0NkWGdnbnFicm9zVkwyei1aWVpkSk5pdDNZS3ZtV21EeHRXZlppU3ZHT21VWmhiYTlsc1g4WENhWVNTdWFLc3g0c0FHbGNpaFcyYmo1bmluVFk2ZTBPdy01LVhyZ0cyb1JuYUxlNHVhYXY3YTFPeDdQd29paDAzWHF2TE9wTmVfb0Rrak9rRk80dm9IdXJDYU9XLXhxdi1JeEJWaG5jV2x1RjJmZktqeXU0dXNiTHJXTHpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
+          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00</t>
+          <t>31/05/2026 04:00</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5770,17 +5770,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00</t>
+          <t>29/05/2026 04:00</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPWmY3TXBIbWxobnFjUi1mTUozS2xCbTlaSGxKX2o0QTExdWszWk5USkR4ZVk0Zk5vcTIxSm9HZDRzazlGVjBDLVE4a2NTTnQ4eHpQM3cyNTFDVDd1aGs0cFhxUVBmbXlaUTNLMjljT0FSRWlMRm1iVkxMYk1uc2Nvd0JZencteGFkLXNFSWxySlhTNkdpemo2Y2N4ZlFOclJPMkNLUDdGU2FrYTJsRjIzdTE3RWVQUnhGbXJpVkJhcWhjclZJaWdXM2dueTFYRjNfMWE5WjBEWEFxUdIB3wFBVV95cUxOdGxrd3ZlRXQ3X0k0Rkx5VDk0OW5yQ0FyZ1A1QW5wTGhXZDA3blVtaVdobkM5YVFBcEhsUUlYRGYwVlVodlF1UmxsbVZaY0c2Z2lScV9hWnlOdlpZYzZDNXVLWWdiU0FvRExxZlQzQ2d3N3lTbk9tY3pXZEpJOWtZaDhOYVhVOXFFWExTVkYyMU5jUnk3VURmS0dMazRJUERGYS1BS2p5MFo5bXg3eFlPcVJtZ1NMQjBYRDFrWmRRbnpRdWlMU0VmaHI3T2tHUGp2b3I3bFZZYk9oWWhDX3pN?oc=5</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado da Qualicoco por excesso de enxofre - UOL Notícias</t>
+          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - gauchazh.clicrbs.com.br</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQX3Vlc2VrZ2dNdkFzaFhqQzlTLV9acFE3LTRSempETklLa25tdDI1NkxtZXFpS3VyREFIVjBVN2VBSGhjR2EyWmhvZ19xV3IxdVpVbkkwdHdwVEx0b2RRUEJaTFlDdkJKOVN0MldteEViTVJocHJsMWxxUmRWM3dqbS1sc1pMUUJGU3ZqTm1EWlhuLXNkMEtjR3EzMVdmYnFnbktyRzVJcEdMZHVvdEFQM3FmeWpMRUFrSVczNHdwVjBVWmMwMUZhdDk1bVI5OHVKbWxfdl9YRHBTeHJIdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
+          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5868,19 +5868,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
+          <t>Grand Prix SENAI 2026 conecta estudantes e grandes indústrias em maratona nacional de inovação - Agência de Notícias da Indústria</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5890,19 +5890,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNazFuZVlIdUdWeE55Y1hySHEyQnpEazJfaU1ING1DVlNVQ21nUWNVb2pBTE43ZlVwc0NkWGdnbnFicm9zVkwyei1aWVpkSk5pdDNZS3ZtV21EeHRXZlppU3ZHT21VWmhiYTlsc1g4WENhWVNTdWFLc3g0c0FHbGNpaFcyYmo1bmluVFk2ZTBPdy01LVhyZ0cyb1JuYUxlNHVhYXY3YTFPeDdQd29paDAzWHF2TE9wTmVfb0Rrak9rRk80dm9IdXJDYU9XLXhxdi1JeEJWaG5jV2x1RjJmZktqeXU0dXNiTHJXTHpn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
+          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5912,19 +5912,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
+          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5934,19 +5934,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5956,19 +5956,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
+          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5978,73 +5978,73 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
+          <t>Anvisa recolhe lote de coco ralado da Qualicoco por excesso de enxofre - UOL Notícias</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>27/05/2026 04:00</t>
+          <t>28/05/2026 04:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQX3Vlc2VrZ2dNdkFzaFhqQzlTLV9acFE3LTRSempETklLa25tdDI1NkxtZXFpS3VyREFIVjBVN2VBSGhjR2EyWmhvZ19xV3IxdVpVbkkwdHdwVEx0b2RRUEJaTFlDdkJKOVN0MldteEViTVJocHJsMWxxUmRWM3dqbS1sc1pMUUJGU3ZqTm1EWlhuLXNkMEtjR3EzMVdmYnFnbktyRzVJcEdMZHVvdEFQM3FmeWpMRUFrSVczNHdwVjBVWmMwMUZhdDk1bVI5OHVKbWxfdl9YRHBTeHJIdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>27/05/2026 04:00</t>
+          <t>28/05/2026 04:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
+          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>27/05/2026 04:00</t>
+          <t>28/05/2026 04:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6056,95 +6056,95 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
+          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>26/05/2026 04:00</t>
+          <t>27/05/2026 04:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
+          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>25/05/2026 04:00</t>
+          <t>27/05/2026 04:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Copa do Calcário define os semifinalistas - FERJ</t>
+          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>25/05/2026 04:00</t>
+          <t>27/05/2026 04:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>25/05/2026 04:00</t>
+          <t>26/05/2026 04:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
+          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
+          <t>Ureia cai pela quinta semana nos portos - agrolink.com.br</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6205,12 +6205,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
+          <t>Copa do Calcário define os semifinalistas - FERJ</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6220,73 +6220,73 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
+          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>23/05/2026 04:00</t>
+          <t>25/05/2026 04:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Casa Criativa CMOC seleciona projetos com impacto social - Terra</t>
+          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>22/05/2026 04:00</t>
+          <t>25/05/2026 04:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQblBlQWhYdmdqY2MyeGdKeVd1SnZySzcwSWpoRDlKRVNhZ1JaZjBRUUI5cXE3S284eXVYZVRDTHl4RkxneEFIdE1mbVkzWlQtZ0gxcHJnclVQTEhSZkRMLXQ2d3RvaHBwb3hKd0VwMGtRcjNRcmJaUC1FTmF4Z0FkYjEwSXR6eWE0Rmo3cHpSbkh0T3VuRGZDMVFIVjFaWGd6Yl9kUy1hVGdSWXJQYlljV1lrUlNPZS1rN2RKZFNld3Z3VlNzaS1MY1AzLTE1MU9ON2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>22/05/2026 04:00</t>
+          <t>25/05/2026 04:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
@@ -6298,29 +6298,29 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
+          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>22/05/2026 04:00</t>
+          <t>23/05/2026 04:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
+          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6330,129 +6330,129 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
+          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>21/05/2026 04:00</t>
+          <t>22/05/2026 04:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
+          <t>Casa Criativa CMOC seleciona projetos com impacto social - Terra</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>21/05/2026 04:00</t>
+          <t>22/05/2026 04:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQblBlQWhYdmdqY2MyeGdKeVd1SnZySzcwSWpoRDlKRVNhZ1JaZjBRUUI5cXE3S284eXVYZVRDTHl4RkxneEFIdE1mbVkzWlQtZ0gxcHJnclVQTEhSZkRMLXQ2d3RvaHBwb3hKd0VwMGtRcjNRcmJaUC1FTmF4Z0FkYjEwSXR6eWE0Rmo3cHpSbkh0T3VuRGZDMVFIVjFaWGd6Yl9kUy1hVGdSWXJQYlljV1lrUlNPZS1rN2RKZFNld3Z3VlNzaS1MY1AzLTE1MU9ON2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
+          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>20/05/2026 04:00</t>
+          <t>22/05/2026 04:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
+          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>20/05/2026 04:00</t>
+          <t>21/05/2026 04:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
+          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>20/05/2026 04:00</t>
+          <t>21/05/2026 04:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
+          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6462,19 +6462,19 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
+          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6484,19 +6484,19 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
+          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6506,337 +6506,337 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
+          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>19/05/2026 04:00</t>
+          <t>20/05/2026 04:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
+          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - agrolink.com.br</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>19/05/2026 04:00</t>
+          <t>20/05/2026 04:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
+          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>19/05/2026 04:00</t>
+          <t>20/05/2026 04:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
+          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>18/05/2026 04:00</t>
+          <t>19/05/2026 04:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
+          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>17/05/2026 14:07</t>
+          <t>19/05/2026 04:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
+          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>15/05/2026 04:00</t>
+          <t>19/05/2026 04:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
+          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>15/05/2026 04:00</t>
+          <t>18/05/2026 04:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>O obstáculo virou o caminho - CNN Brasil</t>
+          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>14/05/2026 04:00</t>
+          <t>17/05/2026 14:07</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
+          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>13/05/2026 04:00</t>
+          <t>15/05/2026 04:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNSFJIZGVZei1nU0tZTXdGeVdSekJlTkd5ajN1d3MwYk5LcmNTMlc1VWJXcjB3S2JGZmY4d2hTQnVBcGdBUjVYT3Z6Vnh0dVRrZFlXY1hEV25xWXBfVThpZkxFSGM4X3dvTjV6bWtMR2FHWTAwdElxNlpzV0RFNmxLMFhxbHRqUkxKNHdPODhMMEVBeHJfa1BpMGZ2a2FqbTQ5UVh1ZlJKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Ureia cai após meses de valorização - Agrolink</t>
+          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>12/05/2026 04:00</t>
+          <t>15/05/2026 04:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
+          <t>O obstáculo virou o caminho - CNN Brasil</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>12/05/2026 04:00</t>
+          <t>14/05/2026 04:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Secultur</t>
+          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>11/05/2026 13:42</t>
+          <t>13/05/2026 04:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNSFJIZGVZei1nU0tZTXdGeVdSekJlTkd5ajN1d3MwYk5LcmNTMlc1VWJXcjB3S2JGZmY4d2hTQnVBcGdBUjVYT3Z6Vnh0dVRrZFlXY1hEV25xWXBfVThpZkxFSGM4X3dvTjV6bWtMR2FHWTAwdElxNlpzV0RFNmxLMFhxbHRqUkxKNHdPODhMMEVBeHJfa1BpMGZ2a2FqbTQ5UVh1ZlJKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>Novo revestimento de ureia controla liberação e reduz perdas - agrolink.com.br</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>11/05/2026 04:00</t>
+          <t>12/05/2026 04:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
+          <t>Ureia cai após meses de valorização - agrolink.com.br</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>11/05/2026 04:00</t>
+          <t>12/05/2026 04:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
+          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Secultur</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>11/05/2026 04:00</t>
+          <t>11/05/2026 13:42</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6858,19 +6858,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
+          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6880,19 +6880,19 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6902,19 +6902,19 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6924,183 +6924,183 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
+          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>10/05/2026 04:00</t>
+          <t>11/05/2026 04:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
+          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>08/05/2026 04:00</t>
+          <t>11/05/2026 04:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
+          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>08/05/2026 04:00</t>
+          <t>11/05/2026 04:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Vazamento de enxofre interdita rodovia Ayrton Senna, em São Paulo - band.com.br</t>
+          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>08/05/2026 04:00</t>
+          <t>10/05/2026 04:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPYzM4TXRIamotWmZsZG83T0prMmNwb0ZRSnVFY3UxTEFqWnJIWVlmLW9Db3VzX1FSaURNN0RodkhTaGw2R0JkcHFIQWEwV2tPN2tUVnRVYzItUkNRUGQ0UFR4ZmZtWmJRbldEVzB1RWxzLVpfamZUUWVEdU9oZ2xMcHE5cFAtZVhvQXcxTjhERXcwWnJhenhjSmFfSk0wRUdJN184RlMwbEU5aWtHN0JOdmxUVXI1ZW1mZjBHUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
+          <t>Vazamento de enxofre interdita rodovia Ayrton Senna, em São Paulo - band.com.br</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>06/05/2026 11:23</t>
+          <t>08/05/2026 04:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPYzM4TXRIamotWmZsZG83T0prMmNwb0ZRSnVFY3UxTEFqWnJIWVlmLW9Db3VzX1FSaURNN0RodkhTaGw2R0JkcHFIQWEwV2tPN2tUVnRVYzItUkNRUGQ0UFR4ZmZtWmJRbldEVzB1RWxzLVpfamZUUWVEdU9oZ2xMcHE5cFAtZVhvQXcxTjhERXcwWnJhenhjSmFfSk0wRUdJN184RlMwbEU5aWtHN0JOdmxUVXI1ZW1mZjBHUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EUA ainda precisam importar ureia - Agrolink</t>
+          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>06/05/2026 04:00</t>
+          <t>08/05/2026 04:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
+          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>06/05/2026 04:00</t>
+          <t>08/05/2026 04:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdHVNT3dGcTBxcUhOdFp4a0NoWW1lZDBQa0xiWEZpYkFoYTZxT09fQTJvNDIzdnpYU1RNbGtrdFVtUUp0bnJrcWRMeXlsX1lJRE5vUXY3RlJJM2VvVGRWTm5aWUhpTzJ0MHZiUW10em1EZzI4bHVmck1CVXdhSEdxVDFfRUIzZkdzN2Qyb1RWWWtiNjZDRlpKYjNra04?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
+          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>06/05/2026 04:00</t>
+          <t>06/05/2026 11:23</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7112,17 +7112,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
+          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>05/05/2026 04:00</t>
+          <t>06/05/2026 04:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdHVNT3dGcTBxcUhOdFp4a0NoWW1lZDBQa0xiWEZpYkFoYTZxT09fQTJvNDIzdnpYU1RNbGtrdFVtUUp0bnJrcWRMeXlsX1lJRE5vUXY3RlJJM2VvVGRWTm5aWUhpTzJ0MHZiUW10em1EZzI4bHVmck1CVXdhSEdxVDFfRUIzZkdzN2Qyb1RWWWtiNjZDRlpKYjNra04?oc=5</t>
         </is>
       </c>
     </row>
@@ -7134,61 +7134,61 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
+          <t>EUA ainda precisam importar ureia - agrolink.com.br</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>04/05/2026 04:00</t>
+          <t>06/05/2026 04:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
+          <t>Alta do enxofre pressiona uso de fosfatado no país - agrolink.com.br</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>04/05/2026 04:00</t>
+          <t>06/05/2026 04:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
+          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>04/05/2026 04:00</t>
+          <t>05/05/2026 04:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQcjJSS2JUOW9EbGNBMlhnOW05Q1NodTh6Sks5a21QYzFJTGRGYnlmamIzMmxfNVNaOXRqQVA1OTg4NENjVHZ6U19FVjZSYjQwOG11Z0o5YW82VGs3ZXRaQWp5UHJqSk0wVHRZcU11R0pZaVpMZ1J4ZC1veVFpd1puc0V5RWdqQWE0VXhicEd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
+          <t>Ureia inicia queda global após disparada dos preços - StoneX</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPNUMtNEYyR21sTTRYZ2Z5UE9XNGJfMmJvYkJaMjc5em5ZVmx5U3hINmg1MVpHZUdHS2hqbzVnOWN2T0tKV0dmeGFvamdFazhzQ0I3RU9Oa2xEbXBGRDNlUHFfemNTLXpOWUpLeVNCMkZjeWxuS3lDdWE0bEpNLTdBNTRzRDQ0QThrWE9sNDdDdW10ZkZfVFVBUE5zb2E5M29EbkdvLUdSOXRlTTEyZkJ2T0l1aw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Ureia inicia queda global após disparada dos preços - StoneX</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - agrolink.com.br</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7254,19 +7254,19 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPNUMtNEYyR21sTTRYZ2Z5UE9XNGJfMmJvYkJaMjc5em5ZVmx5U3hINmg1MVpHZUdHS2hqbzVnOWN2T0tKV0dmeGFvamdFazhzQ0I3RU9Oa2xEbXBGRDNlUHFfemNTLXpOWUpLeVNCMkZjeWxuS3lDdWE0bEpNLTdBNTRzRDQ0QThrWE9sNDdDdW10ZkZfVFVBUE5zb2E5M29EbkdvLUdSOXRlTTEyZkJ2T0l1aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
+          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7276,19 +7276,19 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQcjJSS2JUOW9EbGNBMlhnOW05Q1NodTh6Sks5a21QYzFJTGRGYnlmamIzMmxfNVNaOXRqQVA1OTg4NENjVHZ6U19FVjZSYjQwOG11Z0o5YW82VGs3ZXRaQWp5UHJqSk0wVHRZcU11R0pZaVpMZ1J4ZC1veVFpd1puc0V5RWdqQWE0VXhicEd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
         </is>
       </c>
     </row>
@@ -7310,17 +7310,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
+          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>01/05/2026 04:00</t>
+          <t>04/05/2026 04:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
         </is>
       </c>
     </row>
@@ -7332,39 +7332,39 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 - Valor Econômico</t>
+          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>30/04/2026 04:00</t>
+          <t>04/05/2026 04:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Petrobrás inicia produção de ureia em unidade no Paraná - aepet.org.br</t>
+          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>30/04/2026 04:00</t>
+          <t>04/05/2026 04:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQejlNQk16MUVZMU1zM1JXRjlfOTNFTlo0WTA1b21JZTk3MW9EMm5UUkVsamlubkVMYVhRcEZvdDFJVzJQMXBKVnRZcVFXd3Y2bWhTX1E2UmZGTzBlbkt2NS1rZmNURlF5V0FvRzk2aDN0WktxQW1CSTg1ck9uZnA1OGZkdlQ5R1d4V0NsRWVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
         </is>
       </c>
     </row>
@@ -7376,17 +7376,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
+          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - agrolink.com.br</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>30/04/2026 04:00</t>
+          <t>01/05/2026 04:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
+          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7408,19 +7408,19 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
+          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
+          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 - Valor Econômico</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7508,193 +7508,193 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
+          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>29/04/2026 04:00</t>
+          <t>30/04/2026 04:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
+          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>30/04/2026 04:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Mercado de enxofre corto de compressão varre através da cadeia de suprimentos - Sunsirs</t>
+          <t>Petrobrás inicia produção de ureia em unidade no Paraná - aepet.org.br</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>30/04/2026 04:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBQbnRCaEVzdkRzQ0tXZHFVZWd1cmFPVlJxcDc5VDY4bnRxaUx2YmRBdXdLOW9TaEhfWTk1Vmp2SldCZktYcmRfNzRaLVozOE9pZ3p4NEZEdTZXNmk1a2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQejlNQk16MUVZMU1zM1JXRjlfOTNFTlo0WTA1b21JZTk3MW9EMm5UUkVsamlubkVMYVhRcEZvdDFJVzJQMXBKVnRZcVFXd3Y2bWhTX1E2UmZGTzBlbkt2NS1rZmNURlF5V0FvRzk2aDN0WktxQW1CSTg1ck9uZnA1OGZkdlQ5R1d4V0NsRWVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
+          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>29/04/2026 04:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
+          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>28/04/2026 04:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
+          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>28/04/2026 04:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
+          <t>Mercado de enxofre corto de compressão varre através da cadeia de suprimentos - Sunsirs</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>28/04/2026 04:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBQbnRCaEVzdkRzQ0tXZHFVZWd1cmFPVlJxcDc5VDY4bnRxaUx2YmRBdXdLOW9TaEhfWTk1Vmp2SldCZktYcmRfNzRaLVozOE9pZ3p4NEZEdTZXNmk1a2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
+          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>24/04/2026 04:00</t>
+          <t>27/04/2026 04:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
+          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>22/04/2026 04:00</t>
+          <t>27/04/2026 04:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7706,61 +7706,61 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>22/04/2026 04:00</t>
+          <t>27/04/2026 04:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
+          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>22/04/2026 04:00</t>
+          <t>24/04/2026 04:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
+          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>21/04/2026 18:42</t>
+          <t>22/04/2026 04:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7772,83 +7772,83 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
+          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>20/04/2026 04:00</t>
+          <t>22/04/2026 04:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
+          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>20/04/2026 04:00</t>
+          <t>22/04/2026 04:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQnFTQVFGck1DaWNqWmRkcW1KY3dLTDJRNFRtNlRtREVUdHoyLXZyNWlHS2k1bDlBMzdyQnVOZVhfd2FqUXppTk9BU0Q2azBNcWxGYzlweG5NWVdGR1NpenFnMGdZSDk1QWVtMVdXNllwZElMQWFfZ1Y3R01RWkxSeWJPelZGSkg3dTlNUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
+          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>17/04/2026 04:00</t>
+          <t>21/04/2026 18:42</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>CSN apresenta inovação sustentável no Vale do Café - A Voz da Cidade</t>
+          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>20/04/2026 04:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQW5tN1NZako4UHpaYzVCYklISkM1ZWZxWEJNazdiTmdSdi1aWVBFZXV3bTQxeDZlTHljTWNiblhsUzQ0LWplMTFnU2lCak90d1dLbXRRM1lBZ2xMUGJOUzAyeEFiendSRXI0cFVYMWlZMTZXVXBtZE5VWlJqSFpVbF82S2dKdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7860,51 +7860,51 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
+          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>20/04/2026 04:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQnFTQVFGck1DaWNqWmRkcW1KY3dLTDJRNFRtNlRtREVUdHoyLXZyNWlHS2k1bDlBMzdyQnVOZVhfd2FqUXppTk9BU0Q2azBNcWxGYzlweG5NWVdGR1NpenFnMGdZSDk1QWVtMVdXNllwZElMQWFfZ1Y3R01RWkxSeWJPelZGSkg3dTlNUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
+          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>17/04/2026 04:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Paranaenses trazem bons resultados da Fórmula Truck no Uruguai - Bem Paraná</t>
+          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7914,205 +7914,205 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUUlhSHF6SzZzdW5jYnJaN1dHcGVtR2oxVExheWdtbXlQVWlXSjFLbWFkVGdDZFlUT1ZJTEFqLUhkeFQtdS1QTTdUb2pXWlprYnA1VnVDZ3VFS204Q1hiSThwVFBJZllPVl8yYjRNaWVDalZvcTdfVGVleGN4WW9kYUtJS1l6U0R2anZkT1BGcXlONlZveDYwcTVMVDR6NnE1Z2fSAacBQVVfeXFMUFVRS1k5U1N2RmpuZHVwbnFxRHh6NjBMQUw2dVBEaGE5X2Uydkd5RVRPVlZSRVhCX3FGOW01aExjVW1LazdPWnVULVlJREZBN2JNM0lnTWNfVDAxRnlpUTJSNVJIbEt4Zzg5NWVUak1RNmx6MkQxNmt6ak94N1A3dG1iOXMzOEhyamN0Uk1aazBncGExNnE4N1BmME5lT3RNX0dUc3ZFeW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Fazenda Florença vai promover evento no Dia Mundial do Café - A Voz da Cidade</t>
+          <t>Paranaenses trazem bons resultados da Fórmula Truck no Uruguai - Bem Paraná</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>12/04/2026 04:00</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPQ1hoX081VlZ5bkR3Y21ZeGE0b1BxT0RiRVBxeWtqS3kydDVNTTJzbE5RU1JfdkNFYUFFMm4xYXNNS2QyRlkwb09RR2VaSzFaZGFBQnlUeVBaTkFiY0pwanl1RFMzMkhwSDZzVTBCdGtoTFFzalpOaTVBR1k5R3RSeEwtdlYyNHNTN3hlVW5xZzQ1dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUUlhSHF6SzZzdW5jYnJaN1dHcGVtR2oxVExheWdtbXlQVWlXSjFLbWFkVGdDZFlUT1ZJTEFqLUhkeFQtdS1QTTdUb2pXWlprYnA1VnVDZ3VFS204Q1hiSThwVFBJZllPVl8yYjRNaWVDalZvcTdfVGVleGN4WW9kYUtJS1l6U0R2anZkT1BGcXlONlZveDYwcTVMVDR6NnE1Z2fSAacBQVVfeXFMUFVRS1k5U1N2RmpuZHVwbnFxRHh6NjBMQUw2dVBEaGE5X2Uydkd5RVRPVlZSRVhCX3FGOW01aExjVW1LazdPWnVULVlJREZBN2JNM0lnTWNfVDAxRnlpUTJSNVJIbEt4Zzg5NWVUak1RNmx6MkQxNmt6ak94N1A3dG1iOXMzOEhyamN0Uk1aazBncGExNnE4N1BmME5lT3RNX0dUc3ZFeW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
+          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
+          <t>CSN apresenta inovação sustentável no Vale do Café - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQW5tN1NZako4UHpaYzVCYklISkM1ZWZxWEJNazdiTmdSdi1aWVBFZXV3bTQxeDZlTHljTWNiblhsUzQ0LWplMTFnU2lCak90d1dLbXRRM1lBZ2xMUGJOUzAyeEFiendSRXI0cFVYMWlZMTZXVXBtZE5VWlJqSFpVbF82S2dKdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
+          <t>Fazenda Florença vai promover evento no Dia Mundial do Café - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>12/04/2026 04:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPQ1hoX081VlZ5bkR3Y21ZeGE0b1BxT0RiRVBxeWtqS3kydDVNTTJzbE5RU1JfdkNFYUFFMm4xYXNNS2QyRlkwb09RR2VaSzFaZGFBQnlUeVBaTkFiY0pwanl1RFMzMkhwSDZzVTBCdGtoTFFzalpOaTVBR1k5R3RSeEwtdlYyNHNTN3hlVW5xZzQ1dw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
+          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>09/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
+          <t>Disparada histórica do enxofre pressiona toda a cadeia - agrolink.com.br</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>09/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>Queda da ureia acompanha alívio geopolítico - agrolink.com.br</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>08/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
+          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>08/04/2026 04:00</t>
+          <t>09/04/2026 04:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
+          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>08/04/2026 04:00</t>
+          <t>09/04/2026 04:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
+          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -8178,51 +8178,51 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>07/04/2026 04:00</t>
+          <t>08/04/2026 04:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
+          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>07/04/2026 04:00</t>
+          <t>08/04/2026 04:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8234,61 +8234,61 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
+          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>06/04/2026 04:00</t>
+          <t>08/04/2026 04:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
+          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>06/04/2026 04:00</t>
+          <t>07/04/2026 04:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Transporte de calcário fortalece produção rural em VG - FOLHAMAX</t>
+          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>04/04/2026 04:00</t>
+          <t>07/04/2026 04:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPaEJ5Zkt0Q0dZY21rM3hDSjJndThldFlqWVV2Y3pfTmFfN3VtbGVNZTlmU2tzakN1bUZUclhRdk9NamJpWURucGR1WFNKam5mbHVPY3ZmZ3hRb0pxWm01d1ZFWkJmUzEwLVBHUGhacm5LSjNKNElQY1g3aGJxeHRGeUV6LTlXMkczZERYUU8wdnZzUFhvZjlrVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8300,171 +8300,171 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>01/04/2026 04:00</t>
+          <t>06/04/2026 04:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Biofragane</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
+          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>01/04/2026 04:00</t>
+          <t>06/04/2026 04:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
+          <t>Transporte de calcário fortalece produção rural em VG - FOLHAMAX</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>31/03/2026 04:00</t>
+          <t>04/04/2026 04:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPaEJ5Zkt0Q0dZY21rM3hDSjJndThldFlqWVV2Y3pfTmFfN3VtbGVNZTlmU2tzakN1bUZUclhRdk9NamJpWURucGR1WFNKam5mbHVPY3ZmZ3hRb0pxWm01d1ZFWkJmUzEwLVBHUGhacm5LSjNKNElQY1g3aGJxeHRGeUV6LTlXMkczZERYUU8wdnZzUFhvZjlrVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Biofragane</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
+          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>31/03/2026 04:00</t>
+          <t>01/04/2026 04:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegocio</t>
+          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>30/03/2026 04:00</t>
+          <t>01/04/2026 04:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
+          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>27/03/2026 04:00</t>
+          <t>31/03/2026 04:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
+          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>25/03/2026 08:19</t>
+          <t>31/03/2026 04:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a775a96d6684ab5a5bab1f1d2d20e1a&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
+          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - portaldoagronegocio.com.br</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>25/03/2026 04:00</t>
+          <t>30/03/2026 04:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
         </is>
       </c>
     </row>
@@ -8476,17 +8476,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
+          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>25/03/2026 04:00</t>
+          <t>27/03/2026 04:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
         </is>
       </c>
     </row>
@@ -8498,17 +8498,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>25/03/2026 04:00</t>
+          <t>25/03/2026 08:19</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a77729af9a34f3d9aab837a9f1175b2&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -8520,149 +8520,149 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
+          <t>Ureia dispara 50% em 30 dias - agrolink.com.br</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>23/03/2026 04:00</t>
+          <t>25/03/2026 04:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZGVwSXBCbHh2T2tRbE1KQk9NRFZIQ1JuaUl3S2lKcVZ2bXlhb3dnOHZHRGp4dVgxRU9ObWxMM0hoTFZXQkh4RlJHVktzUUppdGFINFVBeWNRSVVHR1o1eHVpQU1HZTROWmM5REhaa25xYS0wc0p3ckVsZkNmRGp5Ml9Cd055NUxHWkE5OUEyMlM0WmRuT0o5RWNob0NEdmFFUW5qejJpR00ycTdUQjFMWXVTZFpwaWliTTBJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
+          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>21/03/2026 04:00</t>
+          <t>25/03/2026 04:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>20/03/2026 18:35</t>
+          <t>25/03/2026 04:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
+          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>20/03/2026 14:42</t>
+          <t>23/03/2026 04:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZGVwSXBCbHh2T2tRbE1KQk9NRFZIQ1JuaUl3S2lKcVZ2bXlhb3dnOHZHRGp4dVgxRU9ObWxMM0hoTFZXQkh4RlJHVktzUUppdGFINFVBeWNRSVVHR1o1eHVpQU1HZTROWmM5REhaa25xYS0wc0p3ckVsZkNmRGp5Ml9Cd055NUxHWkE5OUEyMlM0WmRuT0o5RWNob0NEdmFFUW5qejJpR00ycTdUQjFMWXVTZFpwaWliTTBJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>20/03/2026 04:00</t>
+          <t>21/03/2026 04:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>20/03/2026 04:00</t>
+          <t>20/03/2026 18:35</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
+          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>19/03/2026 04:00</t>
+          <t>20/03/2026 14:42</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8674,51 +8674,51 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
+          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>19/03/2026 04:00</t>
+          <t>20/03/2026 04:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - casacor.abril.com.br</t>
+          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>19/03/2026 04:00</t>
+          <t>20/03/2026 04:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
+          <t>Disparada histórica do enxofre pressiona fertilizantes - agrolink.com.br</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
+          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - senado.leg.br</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
+          <t>CRA aprova selo para café e alíquota menor sobre calcário - senado.leg.br</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8784,83 +8784,83 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Calcário para uso agrícola deve ficar mais barato - Senado</t>
+          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>18/03/2026 04:00</t>
+          <t>19/03/2026 04:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
+          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>17/03/2026 04:00</t>
+          <t>19/03/2026 04:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
+          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>16/03/2026 04:00</t>
+          <t>19/03/2026 04:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Limestone: a pedra calcária em evidência na arquitetura - Portobello Archtrends</t>
+          <t>Calcário para uso agrícola deve ficar mais barato - senado.leg.br</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>13/03/2026 04:00</t>
+          <t>18/03/2026 04:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8872,17 +8872,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
+          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>13/03/2026 04:00</t>
+          <t>17/03/2026 04:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8894,73 +8894,73 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
+          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>11/03/2026 04:00</t>
+          <t>16/03/2026 04:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
+          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>11/03/2026 04:00</t>
+          <t>13/03/2026 04:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
+          <t>Limestone: a pedra calcária em evidência na arquitetura - Portobello Archtrends</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>11/03/2026 04:00</t>
+          <t>13/03/2026 04:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
+          <t>Agricultores de Corupá já podem solicitar calcário gratuito pelo programa Terra Boa; veja detalhes - JDV - Jornal do Vale</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -8970,19 +8970,19 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBoVzBPSUx1aFltY2FyUnN2Ym1qNExJZkxKckl1bnpsdGwzT2hZdF9PaDN1SHhFV1pQRTNmTWM1TXMtakYyUERmcmRwaVpLRk5kb2JUZ1NobzJVblFVWEp2c0xvVVh2ZDg1WEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
+          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -8992,19 +8992,19 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Agricultores de Corupá já podem solicitar calcário gratuito pelo programa Terra Boa; veja detalhes - JDV - Jornal do Vale</t>
+          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBoVzBPSUx1aFltY2FyUnN2Ym1qNExJZkxKckl1bnpsdGwzT2hZdF9PaDN1SHhFV1pQRTNmTWM1TXMtakYyUERmcmRwaVpLRk5kb2JUZ1NobzJVblFVWEp2c0xvVVh2ZDg1WEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9026,17 +9026,17 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
+          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>10/03/2026 12:14</t>
+          <t>11/03/2026 04:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9048,39 +9048,39 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
+          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>09/03/2026 04:00</t>
+          <t>11/03/2026 04:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
+          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>09/03/2026 04:00</t>
+          <t>11/03/2026 04:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9092,61 +9092,61 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
+          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>06/03/2026 05:00</t>
+          <t>10/03/2026 12:14</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
+          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>06/03/2026 05:00</t>
+          <t>09/03/2026 04:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>"Cal Cruzeiro"</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>06/03/2026 05:00</t>
+          <t>09/03/2026 04:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
         </is>
       </c>
     </row>
@@ -9158,83 +9158,83 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
+          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>05/03/2026 05:00</t>
+          <t>06/03/2026 05:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
+          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>04/03/2026 10:02</t>
+          <t>06/03/2026 05:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
+          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>04/03/2026 05:00</t>
+          <t>06/03/2026 05:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>"Cal Cruzeiro"</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
+          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>04/03/2026 05:00</t>
+          <t>05/03/2026 05:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
         </is>
       </c>
     </row>
@@ -9246,29 +9246,29 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
+          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>04/03/2026 05:00</t>
+          <t>04/03/2026 10:02</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
+          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -9278,239 +9278,239 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
+          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>03/03/2026 05:00</t>
+          <t>04/03/2026 05:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>03/03/2026 05:00</t>
+          <t>04/03/2026 05:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
+          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>27/02/2026 05:00</t>
+          <t>04/03/2026 05:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
+          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>26/02/2026 05:00</t>
+          <t>03/03/2026 05:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
+          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>25/02/2026 05:00</t>
+          <t>03/03/2026 05:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
+          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>25/02/2026 05:00</t>
+          <t>27/02/2026 05:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Mosaic anuncia resultados de 2025 - Revista Cultivar</t>
+          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>25/02/2026 05:00</t>
+          <t>26/02/2026 05:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5rSk81Mmx6dm5KanJ6ZWY1SDBpYzREOE5FeW1YM28tOWxVWUVSRDZEb2thQjNGeFQxREZWMmFnQ09uRzFSMlVmR2h5VlJGRG1EYXpnMjliTkRGQWhFcjZCTF8ta0JkX2FSZ29ISEtrSWJaOU51UGw4c1E4UTB1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado</t>
+          <t>Mosaic anuncia resultados de 2025 - Revista Cultivar</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>25/02/2026 05:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5rSk81Mmx6dm5KanJ6ZWY1SDBpYzREOE5FeW1YM28tOWxVWUVSRDZEb2thQjNGeFQxREZWMmFnQ09uRzFSMlVmR2h5VlJGRG1EYXpnMjliTkRGQWhFcjZCTF8ta0JkX2FSZ29ISEtrSWJaOU51UGw4c1E4UTB1Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
+          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>25/02/2026 05:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
+          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>25/02/2026 05:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
+          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - senado.leg.br</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
         </is>
       </c>
     </row>
@@ -9532,215 +9532,215 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
+          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>19/02/2026 05:00</t>
+          <t>20/02/2026 05:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
+          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>13/02/2026 05:00</t>
+          <t>20/02/2026 05:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - lages.sc.gov.br</t>
+          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>13/02/2026 05:00</t>
+          <t>20/02/2026 05:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
+          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>12/02/2026 05:00</t>
+          <t>19/02/2026 05:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Tecnologia transforma gases de navios em calcário e corta até 95% do CO₂ - Fast Company Brasil</t>
+          <t>Grolime brings high-performance benefits for Scottish soils</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>11/02/2026 05:00</t>
+          <t>14/02/2026 06:00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a77729c5e294553845a66706e125e24&amp;url=https%3a%2f%2fwww.thescottishfarmer.co.uk%2fnews%2f25845962.grolime-brings-high-performance-benefits-scottish-soils%2f&amp;c=18200927900201231641&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Geopolítica: em Foz, pesquisas abrem diálogo sobre multilateralismo e integração latino-americana - h2foz.com.br</t>
+          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>08/02/2026 05:00</t>
+          <t>13/02/2026 05:00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPcUYxX0FCUkdYUGJ6Z2N1Rm5oWWRBNkxyQXhDZTZEaXZ4cDdQSDZxNGp3Tzdnc29JXzg0Unl4Qk1fTEpLS1RyLUdFNHF5WElMWDRtMFJDaWZpRUpJS1laSEd6UTVmbVNBSldwYUstZDdfSFAyT2thT0QxZC1RRW1YMnZoMkFyMzBxTTNpUlo3NXFPTlRzNVVHNzFVVmhpZDFCU2FabFFKbGt5WlA5STVJa2Q3QUZ5WWE2SV9odnBuMFdhOWFCUWlDVmN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Estado da Bahia questiona venda de US$1 bilhão da Equinox Gold - BNamericas</t>
+          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>05/02/2026 05:00</t>
+          <t>13/02/2026 05:00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOTnkzbHIzdDBtODZNZEFjelo2S0UycE01VVYwREI0R25wVjZYUS1VYnJkQU5UbjAzNWhMeDBwMW04VHZpRlcydVQtUDBmNzRYeTlSaFQ4NjRKdEsyRE5mX25rTDUxWnVha3kwNXNmWC1WYnk2aVlmMGxzMTVPUTY5ZWNZWk8tWU55N0ZzeC05NzlpMTdTZDJPQ3BSY0tZdVB3cEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>CMOC e comunidades rurais se unem para dialogar sobre segurança pública - Zap Catalão</t>
+          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>05/02/2026 05:00</t>
+          <t>12/02/2026 05:00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxORzNlMV9FY0ZlTkJzdXNIa01XckhwU1l3RzlOUWpvdnlMNUEwTm9NN210dHJqVGJYSVM0ZXFWbEVKWnZvS1NLZmdnNE1RRjBHc0s2QVhzRWNtN3JtU0ZocXhjRlNCUjd2NzRmdGQ4MzVYSnlxQUxrMnlROS1iMVBHaHIxcWpSMk9SYWJqZFcyNndsX3FCaUpsdTVuSDZLZ2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Parceria entre Governo de Minas e Harsco completa dois anos e beneficia mais de 2 mil agricultores familiares</t>
+          <t>Tecnologia transforma gases de navios em calcário e corta até 95% do CO₂ - Fast Company Brasil</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>04/02/2026 08:38</t>
+          <t>11/02/2026 05:00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a775a96d6684ab5a5bab1f1d2d20e1a&amp;url=https%3a%2f%2fdiariodocomercio.com.br%2fagronegocio%2fparceria-entre-governo-minas-harsco-completa-dois-anos%2f&amp;c=8635377947739043430&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Correção do solo: O uso correto do calcário em solos de cerrado - Notícias Agrícolas</t>
+          <t>Geopolítica: em Foz, pesquisas abrem diálogo sobre multilateralismo e integração latino-americana - h2foz.com.br</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>08/02/2026 05:00</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPdl9xRy1tdHdrNnRjTlctbmpsWDctNEFrZ2FyYUtSVjBSWGlZaUc2cktLWlNJWXJpS2VrYVBtUzhMc3pOUHBERFRvU3RVWXhQbEN0SU1DR2MweTNjbFp5X0tUQXNHdFliLWhPM1UyX0UyaGFnb2F0UGV5VGVSbTA0WVdzNjJ6cHM3SFNPN3NDWWhTY3FlMFhFTFBNZi1Pd3hlUDVXa3U5bm5kbllkc2xTNkQ2X3NhYzFpcFA3X2pBYlBWZzVvTldwblZEV1rSAdIBQVVfeXFMTldVV296U1h2TjROejRMUkVpaWs2eWlKVDJzVjg4eDF4anBCamt3T1FXdW9rOGRsbUg2bEJNZUlBcEVycHdFZHB0OGNGdW10TW1FWEZ2WlJlVHNvbFp5S29QbVZfSGl6SDhQWFk4UF9IM3pXaEVja2NaTi1XdjdVN1VVX3FsYjZMNld4RE5tOFVlTmMyNGdxeFl6RElYQ3ZhcEZxVERKM0FtQkZ5a1NLLUduS18zYkNTQWlvQ3NpdEVFMlhON19iYUJwejA5M0lRZzZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPcUYxX0FCUkdYUGJ6Z2N1Rm5oWWRBNkxyQXhDZTZEaXZ4cDdQSDZxNGp3Tzdnc29JXzg0Unl4Qk1fTEpLS1RyLUdFNHF5WElMWDRtMFJDaWZpRUpJS1laSEd6UTVmbVNBSldwYUstZDdfSFAyT2thT0QxZC1RRW1YMnZoMkFyMzBxTTNpUlo3NXFPTlRzNVVHNzFVVmhpZDFCU2FabFFKbGt5WlA5STVJa2Q3QUZ5WWE2SV9odnBuMFdhOWFCUWlDVmN3?oc=5</t>
         </is>
       </c>
     </row>
@@ -9752,17 +9752,17 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
+          <t>Estado da Bahia questiona venda de US$1 bilhão da Equinox Gold - BNamericas</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>05/02/2026 05:00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOTnkzbHIzdDBtODZNZEFjelo2S0UycE01VVYwREI0R25wVjZYUS1VYnJkQU5UbjAzNWhMeDBwMW04VHZpRlcydVQtUDBmNzRYeTlSaFQ4NjRKdEsyRE5mX25rTDUxWnVha3kwNXNmWC1WYnk2aVlmMGxzMTVPUTY5ZWNZWk8tWU55N0ZzeC05NzlpMTdTZDJPQ3BSY0tZdVB3cEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -9774,149 +9774,149 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>CMOC e comunidades rurais se unem para dialogar sobre segurança pública - Zap Catalão</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>05/02/2026 05:00</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxORzNlMV9FY0ZlTkJzdXNIa01XckhwU1l3RzlOUWpvdnlMNUEwTm9NN210dHJqVGJYSVM0ZXFWbEVKWnZvS1NLZmdnNE1RRjBHc0s2QVhzRWNtN3JtU0ZocXhjRlNCUjd2NzRmdGQ4MzVYSnlxQUxrMnlROS1iMVBHaHIxcWpSMk9SYWJqZFcyNndsX3FCaUpsdTVuSDZLZ2s?oc=5</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
+          <t>Parceria entre Governo de Minas e Harsco completa dois anos e beneficia mais de 2 mil agricultores familiares</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>03/02/2026 05:00</t>
+          <t>04/02/2026 08:38</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a77729af9a34f3d9aab837a9f1175b2&amp;url=https%3a%2f%2fdiariodocomercio.com.br%2fagronegocio%2fparceria-entre-governo-minas-harsco-completa-dois-anos%2f&amp;c=8635377947739043430&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado</t>
+          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>03/02/2026 05:00</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
+          <t>Correção do solo: O uso correto do calcário em solos de cerrado - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>01/02/2026 05:00</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPdl9xRy1tdHdrNnRjTlctbmpsWDctNEFrZ2FyYUtSVjBSWGlZaUc2cktLWlNJWXJpS2VrYVBtUzhMc3pOUHBERFRvU3RVWXhQbEN0SU1DR2MweTNjbFp5X0tUQXNHdFliLWhPM1UyX0UyaGFnb2F0UGV5VGVSbTA0WVdzNjJ6cHM3SFNPN3NDWWhTY3FlMFhFTFBNZi1Pd3hlUDVXa3U5bm5kbllkc2xTNkQ2X3NhYzFpcFA3X2pBYlBWZzVvTldwblZEV1rSAdIBQVVfeXFMTldVV296U1h2TjROejRMUkVpaWs2eWlKVDJzVjg4eDF4anBCamt3T1FXdW9rOGRsbUg2bEJNZUlBcEVycHdFZHB0OGNGdW10TW1FWEZ2WlJlVHNvbFp5S29QbVZfSGl6SDhQWFk4UF9IM3pXaEVja2NaTi1XdjdVN1VVX3FsYjZMNld4RE5tOFVlTmMyNGdxeFl6RElYQ3ZhcEZxVERKM0FtQkZ5a1NLLUduS18zYkNTQWlvQ3NpdEVFMlhON19iYUJwejA5M0lRZzZ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Cientistas descobrem molécula no espaço que indica a origem da vida - CNN Brasil</t>
+          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMUU2NHlFRDNUSjdSQUdPUllVQi1ZbC1UeEhUTEpiQzhITm8teWR1czBGQ2JYaUZDdEdhS2NxUGF2eHU3WjNCQThrOTV3d3BoNC0zOW1oMnhNY0NiMm9ubXdBVk1xa01IcmpMemNaYjhjeTJhV1BJOElvdEQ3bTM5azVVSDZZejdxU0hwb1Jzbnp0OE9ybkFRWjk0bjBqZXJrNllQdXUtRTU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
+          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - senado.leg.br</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
+          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxPd0cwckJ1SE5VRTRFRmZKZS1va0c0S3EwSlEtZnhzUURUbWwtVU9MdE1TLTBSQzV1SDZ2Y2xfQ01KVEZiUS01cmh3OVVYdW9CRWZ0NzV1NTRaZWlYWjQ4U0E1NTNKX3BCTHhOekJTWk9FZVdzcEVOUjFKYXVVZlVtYnR4OG1lN2pPY2gtWm5hRTRuU3hsX29icm4tUy1mNktiM0QyVTZlakktX1FMSWNfRnNRRDltOG5YSVRrT3NuYkI5NEtjNVVjSjJrd0E4UTFIdVBHdnRTa09seU1FUE5PTnpOZlpqaXRPREhKOXM5bTVJMUFiUjVuVnJtQjkxci1XRS14TlBpbktyUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
         </is>
       </c>
     </row>
@@ -9928,61 +9928,61 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Ricaços do ouro vendem minas no Brasil por R$ 5,36 bilhões - A Crítica</t>
+          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>28/01/2026 05:00</t>
+          <t>01/02/2026 05:00</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOdHZONGhzLTExN2VpcWI5TV82OWpVNmZCUmhJTzNybTIzMEtSRGFDTkp4QjZRb09qMW9sakNBc1RFSmxmUVI5SmtPZ1FSQVJVQnY5UU1LdDBlYld6QktSeE9QSTViRGRHajY4aWxTOWhmVndmdkRsbUVzdFcyR3BfNkt2Y0RrV19FLVhoT2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
+          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>27/01/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxPd0cwckJ1SE5VRTRFRmZKZS1va0c0S3EwSlEtZnhzUURUbWwtVU9MdE1TLTBSQzV1SDZ2Y2xfQ01KVEZiUS01cmh3OVVYdW9CRWZ0NzV1NTRaZWlYWjQ4U0E1NTNKX3BCTHhOekJTWk9FZVdzcEVOUjFKYXVVZlVtYnR4OG1lN2pPY2gtWm5hRTRuU3hsX29icm4tUy1mNktiM0QyVTZlakktX1FMSWNfRnNRRDltOG5YSVRrT3NuYkI5NEtjNVVjSjJrd0E4UTFIdVBHdnRTa09seU1FUE5PTnpOZlpqaXRPREhKOXM5bTVJMUFiUjVuVnJtQjkxci1XRS14TlBpbktyUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Agricultores de Rio Preto da Eva recebem 6 toneladas de calcário - Amazonas1</t>
+          <t>Cientistas descobrem molécula no espaço que indica a origem da vida - CNN Brasil</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>25/01/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPUGFSbXJwbzhHMGZTUlM2Q3FIWDlpTExxVUJ2SVB0QlZxQU5laGF1WC1DZ3hpZEt6QnVqX2hvWGZuMC1XZ0dOcHcybkVjaWlyWlBCTkJNREpZX1RpRDZDTV9LRlhIZUV2Ry1pckNHTXM3anVuMU02UHg5QVN6NG4tOWlZU3UxU1VBVV80SEVVMTVsZEcz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMUU2NHlFRDNUSjdSQUdPUllVQi1ZbC1UeEhUTEpiQzhITm8teWR1czBGQ2JYaUZDdEdhS2NxUGF2eHU3WjNCQThrOTV3d3BoNC0zOW1oMnhNY0NiMm9ubXdBVk1xa01IcmpMemNaYjhjeTJhV1BJOElvdEQ3bTM5azVVSDZZejdxU0hwb1Jzbnp0OE9ybkFRWjk0bjBqZXJrNllQdXUtRTU?oc=5</t>
         </is>
       </c>
     </row>
@@ -9994,303 +9994,303 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
+          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - diariodaregiao.com.br</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>23/01/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic paralisa produção de SSP no Brasil por mais 30 dias - Brasil Mineral</t>
+          <t>Ricaços do ouro vendem minas no Brasil por R$ 5,36 bilhões - A Crítica</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>21/01/2026 05:00</t>
+          <t>28/01/2026 05:00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcmlUZDBXN0szYV81b3IyR193M0xrNks3X01wdmhSdjRNRi1DNVgyWGxlZThqU1ZjVVM4bEczaHpJMllVX0lTNjNoYXZNREhJUEhhSGhYRWUyS1pSZnZmcmRCS1d5aHNZeWhJcmdYdlQ2eUZobmRkYXlXY29Od25wU1dPSXRCeXVGVlRqY3Q4RWI5N210THNuSWxZRmVTWDBPLVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOdHZONGhzLTExN2VpcWI5TV82OWpVNmZCUmhJTzNybTIzMEtSRGFDTkp4QjZRb09qMW9sakNBc1RFSmxmUVI5SmtPZ1FSQVJVQnY5UU1LdDBlYld6QktSeE9QSTViRGRHajY4aWxTOWhmVndmdkRsbUVzdFcyR3BfNkt2Y0RrV19FLVhoT2F3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação de produção de fertilizante SSP - CNN Brasil</t>
+          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>21/01/2026 05:00</t>
+          <t>27/01/2026 05:00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUTh0c1hCRzA4emxnNHhfNnYwdTJaWEg3SlRaLW9pNWdFUGY1U2ZDcnZCOTFZRmtveFIzM3RyTmh0Y2k3Y1hubnVLbElqMkItRjJ5N2FzNEcwcGJXTm9DVU9ZN0otV1lQR2dFNDViVGg3QTUxOEtSSnprS1dURDZ1dl9fWlFhNW9Vc2hmRGpxVVI0TDRaMnlGS2VB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - Revista Cultivar</t>
+          <t>Agricultores de Rio Preto da Eva recebem 6 toneladas de calcário - amazonas1.com.br</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>16/01/2026 05:00</t>
+          <t>25/01/2026 05:00</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPUGFSbXJwbzhHMGZTUlM2Q3FIWDlpTExxVUJ2SVB0QlZxQU5laGF1WC1DZ3hpZEt6QnVqX2hvWGZuMC1XZ0dOcHcybkVjaWlyWlBCTkJNREpZX1RpRDZDTV9LRlhIZUV2Ry1pckNHTXM3anVuMU02UHg5QVN6NG4tOWlZU3UxU1VBVV80SEVVMTVsZEcz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Mosaic aponta deterioração do mercado de fertilizantes no Brasil e prevê resultados fracos no trimestre - AgFeed</t>
+          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>16/01/2026 05:00</t>
+          <t>23/01/2026 05:00</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNd2hsY05pajdmUnlUc0QyWi1fMjBfTW1qMU1aT3phMVRVd2tIRm5XcnQxT0t3TXM0MTdDUDNMZjlwNUdzY1hTYmZSdWR2WmdQV0l5cElZV1ZRNlRQdFFZZEhDdGVsYWpoUTNCUnlmdDRweHV5NXNCR25oamcxbGJVLVhrd2hxSU4zb1R0Q0tDbFpWbVpLV0ZMMnVOM1BvaGFQVHczZktiX1hidXVtSGVkZVVoT3NwbkJ5YWlsWEJ3RXpOcml3VWpFY3F4bzF3VHJ1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Passa Sete abre inscrições para pedidos de calcário - radiosobradinho.com.br</t>
+          <t>Mosaic prorroga paralisação de produção de fertilizante SSP - CNN Brasil</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>15/01/2026 05:00</t>
+          <t>21/01/2026 05:00</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNQkVmeU43d3FMWjBLMTZ1SWJnVFZSVXFmT3JmM2dFOTdkeFkxLVNodG1ub3hvWEs2eHR4Z3NMd2c5VkFVU2t0S25XYVVEWXRtTHVkUmdVOFdQVGZ3OGJ3YkNmY2xMeGRyLWgxbktJXzhOUF9uN0FWUUcxSnk2cUtFRk5JQ1NHSXJJRHlwcE9oQUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUTh0c1hCRzA4emxnNHhfNnYwdTJaWEg3SlRaLW9pNWdFUGY1U2ZDcnZCOTFZRmtveFIzM3RyTmh0Y2k3Y1hubnVLbElqMkItRjJ5N2FzNEcwcGJXTm9DVU9ZN0otV1lQR2dFNDViVGg3QTUxOEtSSnprS1dURDZ1dl9fWlFhNW9Vc2hmRGpxVVI0TDRaMnlGS2VB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Como um sabonete de enxofre virou um hit de vendas na Granado - Valor Econômico</t>
+          <t>Mosaic aponta deterioração do mercado de fertilizantes no Brasil e prevê resultados fracos no trimestre - AgFeed</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>14/01/2026 05:00</t>
+          <t>16/01/2026 05:00</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOd0MzT0JQQ0NDVURyWFJKaHdOUDQ5c0sxbUM5RmxYVVFjZ1R3X00xNndfT2lMNWx4VjJfOEx6OFVTZE82bVJKMm1sdGVEeHBtc3pXM0djSllfOHRod01TRUEzdGdtNGIydDVjX3IzeW03Rlk2LUdrTTlfdF9PYzNxU3BYZW84c09pSHV4ZHNIM2VhOWdCQXVzSjhYejBRVWxYeGY2WktaS3NuR08yVnl6YnczMFROYktWUG02NVh2YTVxcVlWcGt5b3NZV2FHUTFjMlJ6T2lQR3dIZnPSAeoBQVVfeXFMTkMwSmdaUTlwTllwcnNxNDVqc2hPRHB5WDdROVdMWXRWaGs3U3M2cmU4MWNnNHFRd2dYeVM0bDNER0pKaTFRTThOcV9nYmNLTmU4TERRWmRsaVpzcmxvSE5xUmtmMldaODY0d2t1a280SFVmMXdCcUJYOENrUkxCcC0yWGVBeUZlYXVQN2lnWS1HdFdvTFIzdWJ5NTY2Tng0UlQ2M2RVTmlQTVNGV3RLVWRZYWxfNUYzZjNwalFfaFBIT212TmtiR1hpYS1rN3lwb2dWQzRvRHdHODdSd1Jrcms5X2wxMzdhaXB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNd2hsY05pajdmUnlUc0QyWi1fMjBfTW1qMU1aT3phMVRVd2tIRm5XcnQxT0t3TXM0MTdDUDNMZjlwNUdzY1hTYmZSdWR2WmdQV0l5cElZV1ZRNlRQdFFZZEhDdGVsYWpoUTNCUnlmdDRweHV5NXNCR25oamcxbGJVLVhrd2hxSU4zb1R0Q0tDbFpWbVpLV0ZMMnVOM1BvaGFQVHczZktiX1hidXVtSGVkZVVoT3NwbkJ5YWlsWEJ3RXpOcml3VWpFY3F4bzF3VHJ1?oc=5</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Combinação Potássio e Enxofre maximiza potencial da soja - Agrolink</t>
+          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - Revista Cultivar</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>13/01/2026 05:00</t>
+          <t>16/01/2026 05:00</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
+          <t>Passa Sete abre inscrições para pedidos de calcário - radiosobradinho.com.br</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>13/01/2026 05:00</t>
+          <t>15/01/2026 05:00</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNQkVmeU43d3FMWjBLMTZ1SWJnVFZSVXFmT3JmM2dFOTdkeFkxLVNodG1ub3hvWEs2eHR4Z3NMd2c5VkFVU2t0S25XYVVEWXRtTHVkUmdVOFdQVGZ3OGJ3YkNmY2xMeGRyLWgxbktJXzhOUF9uN0FWUUcxSnk2cUtFRk5JQ1NHSXJJRHlwcE9oQUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Sibelco</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Sibelco Portugal distinguida a nível nacional e internacional - O Mirante</t>
+          <t>Como um sabonete de enxofre virou um hit de vendas na Granado - Valor Econômico</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>11/01/2026 05:00</t>
+          <t>14/01/2026 05:00</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPVl8tSExZS016cjFOUVA5NVhOYTlEQk1rZ2xPYldkczhvbHZEUlJScWJJTnhDVkVZeF9tWmZEa2lSbWRfdWRyRHh3aVRzZmlvSE1MRmdVSTRhM2JlakFzWUhFbUQyZnRHbUFPRVZUYS1yTjNnS3RTZFNwWmVkeTlOX0tJZXFOT3F2WFh3OVFCNUNRZ2diSG5BNUtxOE1zOWhpbkJhNXJmdXk3Ykd2aW1J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOd0MzT0JQQ0NDVURyWFJKaHdOUDQ5c0sxbUM5RmxYVVFjZ1R3X00xNndfT2lMNWx4VjJfOEx6OFVTZE82bVJKMm1sdGVEeHBtc3pXM0djSllfOHRod01TRUEzdGdtNGIydDVjX3IzeW03Rlk2LUdrTTlfdF9PYzNxU3BYZW84c09pSHV4ZHNIM2VhOWdCQXVzSjhYejBRVWxYeGY2WktaS3NuR08yVnl6YnczMFROYktWUG02NVh2YTVxcVlWcGt5b3NZV2FHUTFjMlJ6T2lQR3dIZnPSAeoBQVVfeXFMTkMwSmdaUTlwTllwcnNxNDVqc2hPRHB5WDdROVdMWXRWaGs3U3M2cmU4MWNnNHFRd2dYeVM0bDNER0pKaTFRTThOcV9nYmNLTmU4TERRWmRsaVpzcmxvSE5xUmtmMldaODY0d2t1a280SFVmMXdCcUJYOENrUkxCcC0yWGVBeUZlYXVQN2lnWS1HdFdvTFIzdWJ5NTY2Tng0UlQ2M2RVTmlQTVNGV3RLVWRZYWxfNUYzZjNwalFfaFBIT212TmtiR1hpYS1rN3lwb2dWQzRvRHdHODdSd1Jrcms5X2wxMzdhaXB3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
+          <t>Combinação Potássio e Enxofre maximiza potencial da soja - agrolink.com.br</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>07/01/2026 05:00</t>
+          <t>13/01/2026 05:00</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
+          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>06/01/2026 05:00</t>
+          <t>13/01/2026 05:00</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Sibelco</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
+          <t>Sibelco Portugal distinguida a nível nacional e internacional - O Mirante</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>30/12/2025 05:00</t>
+          <t>11/01/2026 05:00</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPVl8tSExZS016cjFOUVA5NVhOYTlEQk1rZ2xPYldkczhvbHZEUlJScWJJTnhDVkVZeF9tWmZEa2lSbWRfdWRyRHh3aVRzZmlvSE1MRmdVSTRhM2JlakFzWUhFbUQyZnRHbUFPRVZUYS1yTjNnS3RTZFNwWmVkeTlOX0tJZXFOT3F2WFh3OVFCNUNRZ2diSG5BNUtxOE1zOWhpbkJhNXJmdXk3Ykd2aW1J?oc=5</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
+          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>30/12/2025 05:00</t>
+          <t>07/01/2026 05:00</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN30gHwAUFVX3lxTE8xMV80NEVMcm9zLS1XZ0lVUERHNWczaDQwMVBZOVR2cW5YS3BmUXphdjJPZzJ6amp0dVpjcmo4bG90a1dTb09ncHFiX2ZlS2FCNXN4NktGM0lrQTZyZXhacTFlTjVrQU9kUFNoU2Z0bWhZdVBnaWVuMnRORm16YXNqQzdqX1lLTERqZGdUSk9TUVFrVVZDVnRLY3Z1OXJBaHlRRkt3MTE2R1NMc0VEYkl1S0FKY0xzT0VXWjJEN05XXzFSb3hILWcyamNDUzBuNzJGamQ1WF9PdmdKTi1BQm5KTl9ZNmdaZ3R4cXFzbXZKaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
         </is>
       </c>
     </row>
@@ -10302,83 +10302,83 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Venda de minas de ouro no Brasil por US$ 1 bilhão reacende debate sobre recursos naturais e soberania - MEON</t>
+          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>22/12/2025 05:00</t>
+          <t>06/01/2026 05:00</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQRnFCa2dQWTktSUZxQW1BRnVBdzhNSkxZUWtlUFVjUWFUTWhMU045UTZWcTJTQ2hneE9wQ1NaU0t4ZFE5MHNVN3dMNWh3NlF1UW1RN0lDVDFfSzZmQlpuMWhfdG1sQ19wWmdweGFaWDNOSHFhTnB3aEo1dXBpRmhTWGF1NE9RaVdSY3ozaTdYbjAyUndhVzZEX3ZJNXJyTlVjazJWRkpVcXVDQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
+          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>20/12/2025 05:00</t>
+          <t>30/12/2025 05:00</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
+          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>19/12/2025 05:00</t>
+          <t>30/12/2025 05:00</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN30gHwAUFVX3lxTE8xMV80NEVMcm9zLS1XZ0lVUERHNWczaDQwMVBZOVR2cW5YS3BmUXphdjJPZzJ6amp0dVpjcmo4bG90a1dTb09ncHFiX2ZlS2FCNXN4NktGM0lrQTZyZXhacTFlTjVrQU9kUFNoU2Z0bWhZdVBnaWVuMnRORm16YXNqQzdqX1lLTERqZGdUSk9TUVFrVVZDVnRLY3Z1OXJBaHlRRkt3MTE2R1NMc0VEYkl1S0FKY0xzT0VXWjJEN05XXzFSb3hILWcyamNDUzBuNzJGamQ1WF9PdmdKTi1BQm5KTl9ZNmdaZ3R4cXFzbXZKaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Preço do enxofre deixa mercado de fertilizantes em alerta - AgFeed</t>
+          <t>Venda de minas de ouro no Brasil por US$ 1 bilhão reacende debate sobre recursos naturais e soberania - MEON</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>18/12/2025 05:00</t>
+          <t>22/12/2025 05:00</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNdnJJMlZsR3lYS3FUU0JGenh2VHBURDlOaGFlMTFOaHMzSzVwd0RaN2pPQkhpMGJtM1lFZm1kODU1RXFXcWVkV09uZ1ZtRzlKd0VwOF9RcFl0MW9aNERPU05PVWlxMlRvY1dyMFVfemIySDRPOVotS1pqTmE5WGhNNFB4WTBVeWF1SHh6cUVnODduQ0w2NWplM0paWDFpdXA0cXo3MW1NWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQRnFCa2dQWTktSUZxQW1BRnVBdzhNSkxZUWtlUFVjUWFUTWhMU045UTZWcTJTQ2hneE9wQ1NaU0t4ZFE5MHNVN3dMNWh3NlF1UW1RN0lDVDFfSzZmQlpuMWhfdG1sQ19wWmdweGFaWDNOSHFhTnB3aEo1dXBpRmhTWGF1NE9RaVdSY3ozaTdYbjAyUndhVzZEX3ZJNXJyTlVjazJWRkpVcXVDQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10390,39 +10390,39 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
+          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>20/12/2025 05:00</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>19/12/2025 05:00</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
         </is>
       </c>
     </row>
@@ -10434,29 +10434,29 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
+          <t>Preço do enxofre deixa mercado de fertilizantes em alerta - AgFeed</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>18/12/2025 05:00</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNdnJJMlZsR3lYS3FUU0JGenh2VHBURDlOaGFlMTFOaHMzSzVwd0RaN2pPQkhpMGJtM1lFZm1kODU1RXFXcWVkV09uZ1ZtRzlKd0VwOF9RcFl0MW9aNERPU05PVWlxMlRvY1dyMFVfemIySDRPOVotS1pqTmE5WGhNNFB4WTBVeWF1SHh6cUVnODduQ0w2NWplM0paWDFpdXA0cXo3MW1NWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - mundoba.com.br</t>
+          <t>Alta do enxofre pausa produção de fosfato - agrolink.com.br</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - mundoba.com.br</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
+          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
         </is>
       </c>
     </row>
@@ -10522,39 +10522,39 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
+          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10566,29 +10566,29 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
+          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
+          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -10620,19 +10620,19 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Gigante chinesa compra quatro minas de ouro no Brasil por 863 milhões de euros - Jornal de Notícias</t>
+          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPTWh1d1loQjRUc2ZBZXVkMDdUeElMTVRKc1Z4ZnZERlBhTlJ3LUlrb3VTLUY0XzBLTXozcGJ5LVVlR3hjWkFIVm9tcjdScm11RzgxSWNFZVhNREM2SlBDdlI3RGJpaHRmTzBHaDJuZkRwSDlQbmNtbTZ2MHV4U0ZxeHBrTkdaWm85SXdEVVJ4QmdLbW1hMVE2Y2lhMFM5VDZTejBqMXRYWWNLVXdZeTE1bnRWWmxLb2NQZ3fSAa4BQVVfeXFMT25NQ3lFNTRJSGVNVlJQYjJ2LXVqX2dVaXU3Rkx1cE5XcUdoNlZiZ3BhNG13MFM3TnFNWVBrX0xDQUNxbEw4RjdWN3E4SnVITDItNkJSdW1wRFM1a1dFTEd6SkZ4aUNCZkZjT1oyVUFsa1JIN2liVnV0bHQ2QTVDamlZVFRaYk5nVHJlczViampETVRlYy0yeHhKZkJsOVgzZkZ2bFhTWXpfNmVYWFNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10654,17 +10654,17 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - timesbrasil.com.br</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10676,39 +10676,39 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Gigante chinesa compra quatro minas de ouro no Brasil por 863 milhões de euros - Jornal de Notícias</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPTWh1d1loQjRUc2ZBZXVkMDdUeElMTVRKc1Z4ZnZERlBhTlJ3LUlrb3VTLUY0XzBLTXozcGJ5LVVlR3hjWkFIVm9tcjdScm11RzgxSWNFZVhNREM2SlBDdlI3RGJpaHRmTzBHaDJuZkRwSDlQbmNtbTZ2MHV4U0ZxeHBrTkdaWm85SXdEVVJ4QmdLbW1hMVE2Y2lhMFM5VDZTejBqMXRYWWNLVXdZeTE1bnRWWmxLb2NQZ3fSAa4BQVVfeXFMT25NQ3lFNTRJSGVNVlJQYjJ2LXVqX2dVaXU3Rkx1cE5XcUdoNlZiZ3BhNG13MFM3TnFNWVBrX0xDQUNxbEw4RjdWN3E4SnVITDItNkJSdW1wRFM1a1dFTEd6SkZ4aUNCZkZjT1oyVUFsa1JIN2liVnV0bHQ2QTVDamlZVFRaYk5nVHJlczViampETVRlYy0yeHhKZkJsOVgzZkZ2bFhTWXpfNmVYWFNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
+          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
+          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - timesbrasil.com.br</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - china2brazil.com.br</t>
+          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTDdIZDRmYlIyRXdYek5lTldDN1JQSWZybnVkdW1WblZTbHlfMU1maDh5b05ha2VreS1CSG5iYkxCWl9RWm1nUHYzZUNmSkdMQ1hidUxBeUUwc0dueEthWXRCbWp0eHB6NTlkcFhNZnBNcHlsMnZOdDFZV0pZY0szZnRiTzBOMlJLbl81bFE5LUk2Z3VHaUJHbjl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
+          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews</t>
+          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10874,17 +10874,17 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
+          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>14/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10896,17 +10896,17 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>14/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS?oc=5</t>
         </is>
       </c>
     </row>
@@ -10918,205 +10918,205 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>SUSTENTABILIDADE | CMOC Brasil é reconhecida pelo Selo ODS Brasil 2025 - Brasil Mineral</t>
+          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - China 2 Brazil</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>13/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSzczY2JlaXVTMkliamlDU3cwMU1nTFl5WWotNkFyc2tZckV5ZDl6OG80eEZtTjVOZlp2OThITVZpYVdYcDhGN1p3Yk1VTFRzblhKZGh1cnlsMjZQeHFRMm9lV1VhZGxsMWFTX2J4NV90NFZiZlA0RkRPU3NyWDdQUXJyWWhrNWUtQVFONVM3eUVYLXAzVW1xMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTDdIZDRmYlIyRXdYek5lTldDN1JQSWZybnVkdW1WblZTbHlfMU1maDh5b05ha2VreS1CSG5iYkxCWl9RWm1nUHYzZUNmSkdMQ1hidUxBeUUwc0dueEthWXRCbWp0eHB6NTlkcFhNZnBNcHlsMnZOdDFZV0pZY0szZnRiTzBOMlJLbl81bFE5LUk2Z3VHaUJHbjl3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
+          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>07/12/2025 19:00</t>
+          <t>14/12/2025 05:00</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a775a97b7264c6794f22435bd29f3b8&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Parabenos e dióxido de enxofre fazem mal à saúde? Conheça esses conservantes - Olhar Digital</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>05/12/2025 05:00</t>
+          <t>14/12/2025 05:00</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNdWF2bGw2UWZLUTRmVzV4TE1UYlVkQjl6Q1NQMFZ6VVBsZzBMYUk0aWhfYmp2czBONHFCejlJeFVfNGVQQ3RDd2JuTUhJdFFPbHgzSV8tRU9BZTk2aS1ncFZDOUhBZkV4TGh0ZmthdnVjRnFwQng5VGhUQW9MZENYVG9ReDBGTC1IS0VtZkhCaS02VG5wV21UQ2xvc2xva1NHQWh6M1M5cG5CZHk3UkFXMjNpdllxeVQ4TW84bHFWcWhUMzlOR0tOckRua0w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic investe R$ 350 mil em projetos de inovação para melhoria operacional - Brasil Mineral</t>
+          <t>SUSTENTABILIDADE | CMOC Brasil é reconhecida pelo Selo ODS Brasil 2025 - Brasil Mineral</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>02/12/2025 05:00</t>
+          <t>13/12/2025 05:00</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNenNPSXRyeVo2djFmWk9EQlFuWTdfZkdwb3EzUHdreWpqM3E1dk9meG9SYXZncnptdDBTV0xHUnpVSGVlXzZETUc1eEFWNWlEZnRTd0pkMEtaVm9GQkRtUXd6WEYwcmthZDZtQ2h3ckx3TGNLRFJVOFBPZXpHWXlESzdqbVdwTGg0X3JwWkRfOTlBVERmSTM2VkdMUkwwMDdTandqbTVlSFB3Z0MtZUVacmpoQmlhUHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSzczY2JlaXVTMkliamlDU3cwMU1nTFl5WWotNkFyc2tZckV5ZDl6OG80eEZtTjVOZlp2OThITVZpYVdYcDhGN1p3Yk1VTFRzblhKZGh1cnlsMjZQeHFRMm9lV1VhZGxsMWFTX2J4NV90NFZiZlA0RkRPU3NyWDdQUXJyWWhrNWUtQVFONVM3eUVYLXAzVW1xMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
+          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>02/12/2025 05:00</t>
+          <t>07/12/2025 19:00</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a77729c5e294553845a66706e125e24&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
+          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>26/11/2025 03:44</t>
+          <t>02/12/2025 05:00</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
+          <t>FERTILIZANTES | Mosaic investe R$ 350 mil em projetos de inovação para melhoria operacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>24/11/2025 05:00</t>
+          <t>02/12/2025 05:00</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNenNPSXRyeVo2djFmWk9EQlFuWTdfZkdwb3EzUHdreWpqM3E1dk9meG9SYXZncnptdDBTV0xHUnpVSGVlXzZETUc1eEFWNWlEZnRTd0pkMEtaVm9GQkRtUXd6WEYwcmthZDZtQ2h3ckx3TGNLRFJVOFBPZXpHWXlESzdqbVdwTGg0X3JwWkRfOTlBVERmSTM2VkdMUkwwMDdTandqbTVlSFB3Z0MtZUVacmpoQmlhUHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
+          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>19/11/2025 05:00</t>
+          <t>26/11/2025 03:44</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
+          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>19/11/2025 05:00</t>
+          <t>24/11/2025 05:00</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
+          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
         </is>
       </c>
     </row>
@@ -11138,61 +11138,61 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
+          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>17/11/2025 13:00</t>
+          <t>19/11/2025 05:00</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a775a96d6684ab5a5bab1f1d2d20e1a&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
+          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>17/11/2025 05:00</t>
+          <t>19/11/2025 05:00</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Alta do enxofre supera 130% em 2025 - Agrolink</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>11/11/2025 05:00</t>
+          <t>17/11/2025 13:00</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a77729af9a34f3d9aab837a9f1175b2&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -11204,369 +11204,369 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
+          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>08/11/2025 05:00</t>
+          <t>17/11/2025 05:00</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
+          <t>Alta do enxofre supera 130% em 2025 - agrolink.com.br</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>30/10/2025 04:00</t>
+          <t>11/11/2025 05:00</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
+          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>30/10/2025 04:00</t>
+          <t>08/11/2025 05:00</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
+          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>27/10/2025 04:00</t>
+          <t>30/10/2025 04:00</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
+          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>22/10/2025 10:56</t>
+          <t>30/10/2025 04:00</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a775a97b7264c6794f22435bd29f3b8&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Especialistas registram a maior coruja do continente que come até gambás e coalas - Revista Fórum</t>
+          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>20/10/2025 04:00</t>
+          <t>27/10/2025 04:00</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOZWZIam82STB1M05WMm45bHNjdVJBTl9rRU9zanpRMV9XM0ZXbERYTmFJVVF4M25ZSlVsTWNTVEtTZmR1cXI0REt4SnU2Y3ZyaGNiUTVNenlyNXJHMnhMNTVnbHNnS2FqQjVLZTNvYTN3ZzZaYkplc21fUzB2MGZSM2tvQ0FXSnZpbEJWOG9nRmM0ME1sYnU3R3Zod1hyVzRpRGd4NVZmTjZNZ051dDFkY0FOeVZEeWVRYWtVUFlLSGFLOWowQ2ticnFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Após casos de metanol, cresce busca por regularização da cachaça em MG - Rádio Itatiaia</t>
+          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>15/10/2025 04:00</t>
+          <t>22/10/2025 10:56</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPdXJKTTRWVzZzUm0zSkpRRVJvRXpBQnNQRlg2YUk5MjFSWjhFenlIeHlmYklmS3YyS3A1TFhYSlNab080RHpmcndRckQ5bHl0Yk9aYzRtVkQzTFRiTGo3S05tU3QzcVluYnhZSEk4LXZDdDlfX2JTZFZnekVxVTdnWmtzanhxSkRHcjJDT2YwUERObklaSWgxU0lzYUNoSmF2NlBGbjF3?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a77729c5e294553845a66706e125e24&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>De 100 mil a 1,2 milhão: UGC faz sabonete de enxofre da Granado multiplicar as vendas - Mundo do Marketing</t>
+          <t>Especialistas registram a maior coruja do continente que come até gambás e coalas - revistaforum.com.br</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>13/10/2025 04:00</t>
+          <t>20/10/2025 04:00</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTWprTW9RT3lxQkVOTjZ3QzVvX2R0RHhCZUxFeE1BNGtMY3VKc1Z4NWViSEYyLXdFQnRkWlYwTEZSOHg4UHpQLTJ3RDEySk9Ld2xkaGp4WnVLQWUtcFdrVzcyQ01pUGxfS2lwbzNERGp3WVdYYmdTd2h6SUxVdEhnUHdDRG5Hb2lRZjlBNUQ5QU1MYnlDV3kyRHpFR3lRcXNMa2xDMTR6Y2ZSaE1JczI2RkpENGU1VE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOZWZIam82STB1M05WMm45bHNjdVJBTl9rRU9zanpRMV9XM0ZXbERYTmFJVVF4M25ZSlVsTWNTVEtTZmR1cXI0REt4SnU2Y3ZyaGNiUTVNenlyNXJHMnhMNTVnbHNnS2FqQjVLZTNvYTN3ZzZaYkplc21fUzB2MGZSM2tvQ0FXSnZpbEJWOG9nRmM0ME1sYnU3R3Zod1hyVzRpRGd4NVZmTjZNZ051dDFkY0FOeVZEeWVRYWtVUFlLSGFLOWowQ2ticnFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
+          <t>Após casos de metanol, cresce busca por regularização da cachaça em MG - Rádio Itatiaia</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>13/10/2025 04:00</t>
+          <t>15/10/2025 04:00</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPdXJKTTRWVzZzUm0zSkpRRVJvRXpBQnNQRlg2YUk5MjFSWjhFenlIeHlmYklmS3YyS3A1TFhYSlNab080RHpmcndRckQ5bHl0Yk9aYzRtVkQzTFRiTGo3S05tU3QzcVluYnhZSEk4LXZDdDlfX2JTZFZnekVxVTdnWmtzanhxSkRHcjJDT2YwUERObklaSWgxU0lzYUNoSmF2NlBGbjF3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
+          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>10/10/2025 04:00</t>
+          <t>13/10/2025 04:00</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
+          <t>De 100 mil a 1,2 milhão: UGC faz sabonete de enxofre da Granado multiplicar as vendas - mundodomarketing.com.br</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>09/10/2025 04:00</t>
+          <t>13/10/2025 04:00</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTWprTW9RT3lxQkVOTjZ3QzVvX2R0RHhCZUxFeE1BNGtMY3VKc1Z4NWViSEYyLXdFQnRkWlYwTEZSOHg4UHpQLTJ3RDEySk9Ld2xkaGp4WnVLQWUtcFdrVzcyQ01pUGxfS2lwbzNERGp3WVdYYmdTd2h6SUxVdEhnUHdDRG5Hb2lRZjlBNUQ5QU1MYnlDV3kyRHpFR3lRcXNMa2xDMTR6Y2ZSaE1JczI2RkpENGU1VE0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
+          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>01/10/2025 04:00</t>
+          <t>10/10/2025 04:00</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
+          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>21/09/2025 04:00</t>
+          <t>09/10/2025 04:00</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
+          <t>Lhoist abre inscrições para o Programa Jovem Aprendiz 2026 em Arcos - Arcos Notícias</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>15/09/2025 04:00</t>
+          <t>03/10/2025 08:14</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPOGs0MF9ObWVia181OG5TRmxlNmswYjA4LVZUNjdNSko5akptRGRFX2w4R3Yzam9aM24xazdsUU1PbjRqOXFNbDF6LWhscllMYWJYVUlPVExVSWptRUNrY3J6YWZYdEtqUjNyR0tIb1B2bkVLRGdrMzg5NzJ2SVpzYzVhdlhFUm1uNHRWY2xYX1VOSUp5dkVqc1hUX01GWjFaQWxYTzRRMUdOOTIxb0I4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxORnRTMVVoUTk0Q1JIRy1YYVFTWU9VWDlZa2hjS2g3bzFQNkY3aHVLQ1d3eVdoZHJIeENMV3AybG1JaTBuVGFNYjBGS0xlSGowQkEtVkt6X216WHJQNzdKcHR6YlBuQTNXUHJhWFJSVUlfZlZFYWhkRl9MaWZWMWNibi1OSUFjUDA3YWp6NWtINnYyU1FUVmdfVUxXLTdHSTR6cGNUaE1Ra0FyeThvdExFSkNaTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
+          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>07/09/2025 14:00</t>
+          <t>01/10/2025 04:00</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a775a96d6684ab5a5bab1f1d2d20e1a&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - Revista Cultivar</t>
+          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>05/09/2025 04:00</t>
+          <t>21/09/2025 04:00</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Fundação Dirce Figueiredo chega a Arcos com escola de música gratuita para crianças e jovens - Portal Arcos</t>
+          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>03/09/2025 04:00</t>
+          <t>15/09/2025 04:00</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNaWNLMVJaSWN0MFp5MEstSjZfU1RwZkF3NmxtYjVGRHdRMmllcVJUZTk1enJDdkQ2OGp6Y1A2VHBaeUlyclhMdlFSaHBMVnRqR2RYaHF2Vmx6M0FHZjU3ZnkyUWlxYkJ3TWZRdmxFYmFFTUcyYlEzOGVHSmNScnhhbHZxXzc4aUUxTXhYZjd5Q3lsb01XQTliSS00c053NGk4MnlYYlFpMzdCVU4wTGpVMTZuT1cySEtYLVVRQ3BGakJGa3lUS1Y4dWtJQy1nNHpGd0pF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPOGs0MF9ObWVia181OG5TRmxlNmswYjA4LVZUNjdNSko5akptRGRFX2w4R3Yzam9aM24xazdsUU1PbjRqOXFNbDF6LWhscllMYWJYVUlPVExVSWptRUNrY3J6YWZYdEtqUjNyR0tIb1B2bkVLRGdrMzg5NzJ2SVpzYzVhdlhFUm1uNHRWY2xYX1VOSUp5dkVqc1hUX01GWjFaQWxYTzRRMUdOOTIxb0I4?oc=5</t>
         </is>
       </c>
     </row>
@@ -11578,17 +11578,17 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
+          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>02/09/2025 14:00</t>
+          <t>07/09/2025 14:00</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a775a96d6684ab5a5bab1f1d2d20e1a&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a77729af9a34f3d9aab837a9f1175b2&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -11600,81 +11600,169 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
+          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - Revista Cultivar</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>02/09/2025 04:00</t>
+          <t>05/09/2025 04:00</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
+          <t>Fundação Dirce Figueiredo chega a Arcos com escola de música gratuita para crianças e jovens - Portal Arcos</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>03/09/2025 04:00</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNaWNLMVJaSWN0MFp5MEstSjZfU1RwZkF3NmxtYjVGRHdRMmllcVJUZTk1enJDdkQ2OGp6Y1A2VHBaeUlyclhMdlFSaHBMVnRqR2RYaHF2Vmx6M0FHZjU3ZnkyUWlxYkJ3TWZRdmxFYmFFTUcyYlEzOGVHSmNScnhhbHZxXzc4aUUxTXhYZjd5Q3lsb01XQTliSS00c053NGk4MnlYYlFpMzdCVU4wTGpVMTZuT1cySEtYLVVRQ3BGakJGa3lUS1Y4dWtJQy1nNHpGd0pF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
+          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>02/09/2025 14:00</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a77729af9a34f3d9aab837a9f1175b2&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
+          <t>calcario agricola</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - ufla.br</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>02/09/2025 04:00</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>CMOC</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>01/09/2025 04:00</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>CMOC</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>01/09/2025 04:00</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>agricultural lime</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Spreading Ag Lime for Food Plots | Improving Deer Habitat on Our Southern Illinois Farm</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>18/08/2025 14:00</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a77729c5e294553845a66706e125e24&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
           <t>Carmeuse</t>
         </is>
       </c>
-      <c r="B512" t="inlineStr">
+      <c r="B516" t="inlineStr">
         <is>
           <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr">
+      <c r="C516" t="inlineStr">
         <is>
           <t>15/08/2025 04:00</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr">
+      <c r="D516" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
         </is>
